--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,16 +500,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -537,20 +538,25 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>改动内容</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>前端技术</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>后端技术</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>是否有数据库</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -574,20 +580,25 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>全站优化：消除前端 4 处重复 WebSocket 逻辑与死代码，统一连接/任务工具/常量，增加 ErrorBoundary；后端事件契约规范化、记录模型成本、限制并发</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
           <t>提取共用 useWorkspaceSocket；删除死代码(SystemStatus/SoftwareDock/selectConsoleAgents)；新增 ErrorBoundary；常量集中 constants.ts；任务工具去重 task-utils.ts；fetchedRef 防护</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>TaskStepEventPayload Schema 替代手写 dict；LiteLLM 响应提取成本；并发控制(max 3, 429)；receipt 标注预留</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>前端测试 2→28；净减 237 行</t>
         </is>
@@ -616,15 +627,20 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
+          <t>README 全量翻译</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>全量翻译</t>
         </is>
@@ -648,20 +664,25 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>README 风格重写，含架构图/决策记录</t>
+          <t>README 风格重写，加入架构图与关键决策记录</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>README 结构重排、徽章、ASCII 架构图</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>资深工程师口吻</t>
         </is>
@@ -685,20 +706,25 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
+          <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
           <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>是(provider_credentials)</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Key 永不在列表回传</t>
         </is>
@@ -722,20 +748,25 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>start.bat / start.ps1 一键启动</t>
+          <t>新增 Windows 一键启动脚本</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>start.bat / start.ps1</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Docker Compose 封装</t>
         </is>
@@ -759,22 +790,27 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>next.config 写死 output:standalone 导致 dev 端口不响应</t>
+          <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
+          <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>改 env 按需启用</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>仅生产 Docker 构建启用</t>
         </is>
       </c>
     </row>
@@ -796,20 +832,25 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>自定义模型添加/删除 UI；眼睛图标切换失效修复(undefined 与 React 批处理冲突)</t>
+          <t>新增自定义模型接入（任意 provider/model + fallback 降级）；修复 API Key 眼睛图标切换失效</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>自定义模型添加/删除 UI +「自定义」徽章；眼睛图标切换修复(undefined 与 React 批处理冲突)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>CustomModelConfig 模型；/api/custom-models；chat_completion 自定义解析；修按 name 查 PK bug</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>是(custom_model_configs)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>后端 37→40</t>
         </is>
@@ -833,20 +874,25 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>README 补充「模型与密钥管理」章节</t>
+          <t>README 补充「模型与密钥管理」章节，更新测试数</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
+          <t>README 章节补充</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>测试数 40/28</t>
         </is>
@@ -870,22 +916,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>启动脚本 UTF-8 中文被 cmd/PowerShell 按 ANSI 解析乱码</t>
+          <t>修复一键启动脚本中文乱码（UTF-8 被 cmd/PowerShell 按 ANSI 解析）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>脚本消息改纯 ASCII</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>改纯 ASCII</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>跨代码页安全</t>
         </is>
       </c>
     </row>
@@ -907,22 +958,27 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>设置页表单黑底黑字</t>
+          <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
+          <t>text-foreground 修复</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>text-foreground 修复</t>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -944,22 +1000,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>表单字段文字改纯白</t>
+          <t>设置页表单字段文字改纯白，提升可读性</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>text-white / white/90 / 占位符 white/40</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>text-white</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -981,22 +1042,27 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>点眼睛无法显示已保存 Key(保存后清空+Key 不回传)</t>
+          <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
+          <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
           <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>眼睛点击拉取真实 Key 填充</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>显式操作才返回 Key，列表仍不回传</t>
         </is>
       </c>
     </row>
@@ -1018,20 +1084,25 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>API Key 只保留 DeepSeek 预设；「添加厂商」表单；厂商名 title-case</t>
+          <t>API Key 管理收敛为仅 DeepSeek 预设，用户可自行添加任意厂商的 API</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>「添加厂商」表单(任意厂商名+Key)；厂商名 title-case；移除其余预设</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>移除 Provider 白名单；/models/providers/status 只显示 deepseek+DB 厂商</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>否(复用 provider_credentials)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>后端 40→42</t>
         </is>
@@ -1060,24 +1131,71 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
+          <t>表格 + 维护约定</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>建立本表，后续实时填写</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:15</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>C-015</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>变更追踪表新增「改动内容」列，明确记录每次改了什么</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>表结构更新(PRD.md + Excel)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>业务描述与前后端技术分离</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:G16"/>
+  <autoFilter ref="A2:H17"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
         <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -103,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,14 +115,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -500,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -605,555 +594,555 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-01 20:31</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>C-002</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>README 全文中文化</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>README 全量翻译</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>全量翻译</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>README 更新本轮优化详情</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>README 章节补充</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>测试数 37/28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>2026-08-01 20:33</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>C-003</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>README 全文中文化</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>README 全量翻译</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>全量翻译</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>2026-08-01 20:37</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>C-003</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>C-004</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>README 风格重写，加入架构图与关键决策记录</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>README 结构重排、徽章、ASCII 架构图</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>资深工程师口吻</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-01 21:17</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>C-004</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>是(provider_credentials)</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Key 永不在列表回传</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>2026-08-01 21:17</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>C-005</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>是(provider_credentials)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Key 永不在列表回传</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>2026-08-01 21:20</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>C-005</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>C-006</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>新增 Windows 一键启动脚本</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>start.bat / start.ps1</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Docker Compose 封装</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-02 12:22</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>C-006</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>BUG</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>仅生产 Docker 构建启用</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Docker Compose 封装；自动复制 .env + 等健康</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>2026-08-02 12:22</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>C-007</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>仅生产 Docker 构建启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>2026-08-02 23:28</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>C-007</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>新增自定义模型接入（任意 provider/model + fallback 降级）；修复 API Key 眼睛图标切换失效</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>自定义模型添加/删除 UI +「自定义」徽章；眼睛图标切换修复(undefined 与 React 批处理冲突)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>CustomModelConfig 模型；/api/custom-models；chat_completion 自定义解析；修按 name 查 PK bug</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>是(custom_model_configs)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>后端 37→40</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-02 23:33</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>C-008</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>README 补充「模型与密钥管理」章节，更新测试数</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>README 章节补充</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>测试数 40/28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>2026-08-02 23:33</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>C-009</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>README 补充「模型与密钥管理」章节，更新测试数</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>README 章节补充</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>测试数 40/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>2026-08-02 23:36</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>C-009</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>C-010</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>修复一键启动脚本中文乱码（UTF-8 被 cmd/PowerShell 按 ANSI 解析）</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>脚本消息改纯 ASCII</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>跨代码页安全</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-03 13:06</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>C-010</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>BUG</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>text-foreground 修复</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>2026-08-03 13:06</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>C-011</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>text-foreground 修复</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>2026-08-03 13:10</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>C-011</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>C-012</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>设置页表单字段文字改纯白，提升可读性</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>text-white / white/90 / 占位符 white/40</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-03 13:37</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>C-012</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>BUG</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>显式操作才返回 Key，列表仍不回传</t>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>2026-08-03 13:37</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>显式操作才返回 Key，列表仍不回传</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>2026-08-03 13:50</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>C-013</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>C-014</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>API Key 管理收敛为仅 DeepSeek 预设，用户可自行添加任意厂商的 API</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>「添加厂商」表单(任意厂商名+Key)；厂商名 title-case；移除其余预设</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>移除 Provider 白名单；/models/providers/status 只显示 deepseek+DB 厂商</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>否(复用 provider_credentials)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>后端 40→42</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-03 14:05</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>C-014</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>新增 docs/PRD.md 变更追踪表</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>表格 + 维护约定</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>建立本表，后续实时填写</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 14:15</t>
+          <t>2026-08-03 13:56</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1161,39 +1150,123 @@
           <t>C-015</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>新增 docs/PRD.md 变更追踪表</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>表格 + 维护约定</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>建立本表，后续改动由脚本实时生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:59</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>C-016</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>新增 Excel 变更追踪工作簿</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>openpyxl 生成脚本</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>表结构含颜色/冻结/筛选</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:01</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
           <t>变更追踪表新增「改动内容」列，明确记录每次改了什么</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>表结构更新(PRD.md + Excel)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>业务描述与前后端技术分离</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H17"/>
+  <autoFilter ref="A2:H19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -722,7 +722,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 21:17</t>
+          <t>2026-08-01 20:55</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -737,34 +737,34 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
+          <t>前端视觉与响应式优化，新增通讯录 /contacts 页面与 Agent 头像组件</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
+          <t>新增 agent-portrait.tsx、contacts-page.tsx(/contacts 路由)；agent-gallery/status-panel/app-sidebar/chat 组件重构；globals.css 视觉令牌与响应式优化</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>是(provider_credentials)</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Key 永不在列表回传</t>
+          <t>1203 插入/471 删除，21 文件；位于独立主线(原 main)，当前分支强推覆盖 origin/main 后未合入</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 21:20</t>
+          <t>2026-08-01 21:17</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -779,34 +779,34 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>新增 Windows 一键启动脚本</t>
+          <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>start.bat / start.ps1</t>
+          <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是(provider_credentials)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Docker Compose 封装；自动复制 .env + 等健康</t>
+          <t>Key 永不在列表回传</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02 12:22</t>
+          <t>2026-08-01 21:20</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -814,19 +814,19 @@
           <t>C-007</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>BUG</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
+          <t>新增 Windows 一键启动脚本</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
+          <t>start.bat / start.ps1</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>仅生产 Docker 构建启用</t>
+          <t>Docker Compose 封装；自动复制 .env + 等健康</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02 23:28</t>
+          <t>2026-08-02 12:22</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -856,41 +856,41 @@
           <t>C-008</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Requirement</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>新增自定义模型接入（任意 provider/model + fallback 降级）；修复 API Key 眼睛图标切换失效</t>
+          <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>自定义模型添加/删除 UI +「自定义」徽章；眼睛图标切换修复(undefined 与 React 批处理冲突)</t>
+          <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>CustomModelConfig 模型；/api/custom-models；chat_completion 自定义解析；修按 name 查 PK bug</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>是(custom_model_configs)</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>后端 37→40</t>
+          <t>仅生产 Docker 构建启用</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02 23:33</t>
+          <t>2026-08-02 23:28</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -898,41 +898,41 @@
           <t>C-009</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>README 补充「模型与密钥管理」章节，更新测试数</t>
+          <t>新增自定义模型接入（任意 provider/model + fallback 降级）；修复 API Key 眼睛图标切换失效</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>README 章节补充</t>
+          <t>自定义模型添加/删除 UI +「自定义」徽章；眼睛图标切换修复(undefined 与 React 批处理冲突)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CustomModelConfig 模型；/api/custom-models；chat_completion 自定义解析；修按 name 查 PK bug</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是(custom_model_configs)</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>测试数 40/28</t>
+          <t>后端 37→40</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02 23:36</t>
+          <t>2026-08-02 23:33</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -940,19 +940,19 @@
           <t>C-010</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>BUG</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>修复一键启动脚本中文乱码（UTF-8 被 cmd/PowerShell 按 ANSI 解析）</t>
+          <t>README 补充「模型与密钥管理」章节，更新测试数</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>脚本消息改纯 ASCII</t>
+          <t>README 章节补充</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -967,14 +967,14 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>跨代码页安全</t>
+          <t>测试数 40/28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:06</t>
+          <t>2026-08-02 23:36</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
+          <t>修复一键启动脚本中文乱码（UTF-8 被 cmd/PowerShell 按 ANSI 解析）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>text-foreground 修复</t>
+          <t>脚本消息改纯 ASCII</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1009,14 +1009,14 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>跨代码页安全</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:10</t>
+          <t>2026-08-03 13:06</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>设置页表单字段文字改纯白，提升可读性</t>
+          <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>text-white / white/90 / 占位符 white/40</t>
+          <t>text-foreground 修复</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:37</t>
+          <t>2026-08-03 13:10</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
+          <t>设置页表单字段文字改纯白，提升可读性</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
+          <t>text-white / white/90 / 占位符 white/40</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1093,14 +1093,14 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>显式操作才返回 Key，列表仍不回传</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:50</t>
+          <t>2026-08-03 13:37</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1108,41 +1108,41 @@
           <t>C-014</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Requirement</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>API Key 管理收敛为仅 DeepSeek 预设，用户可自行添加任意厂商的 API</t>
+          <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>「添加厂商」表单(任意厂商名+Key)；厂商名 title-case；移除其余预设</t>
+          <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>移除 Provider 白名单；/models/providers/status 只显示 deepseek+DB 厂商</t>
+          <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>否(复用 provider_credentials)</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>后端 40→42</t>
+          <t>显式操作才返回 Key，列表仍不回传</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:56</t>
+          <t>2026-08-03 13:50</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1150,41 +1150,41 @@
           <t>C-015</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>新增 docs/PRD.md 变更追踪表</t>
+          <t>API Key 管理收敛为仅 DeepSeek 预设，用户可自行添加任意厂商的 API</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>表格 + 维护约定</t>
+          <t>「添加厂商」表单(任意厂商名+Key)；厂商名 title-case；移除其余预设</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>移除 Provider 白名单；/models/providers/status 只显示 deepseek+DB 厂商</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否(复用 provider_credentials)</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>建立本表，后续改动由脚本实时生成</t>
+          <t>后端 40→42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 13:59</t>
+          <t>2026-08-03 13:56</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>新增 Excel 变更追踪工作簿</t>
+          <t>新增 docs/PRD.md 变更追踪表</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>openpyxl 生成脚本</t>
+          <t>表格 + 维护约定</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1219,54 +1219,138 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>表结构含颜色/冻结/筛选</t>
+          <t>建立本表，后续改动由脚本实时生成</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>2026-08-03 13:59</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>新增 Excel 变更追踪工作簿</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>openpyxl 生成脚本</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>表结构含颜色/冻结/筛选</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>2026-08-03 14:01</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>C-017</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>C-018</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>变更追踪表新增「改动内容」列，明确记录每次改了什么</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>表结构更新(PRD.md + Excel)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>业务描述与前后端技术分离</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:04</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>C-019</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>变更追踪表改为从 git history 自动生成</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>generate_change_log.py（爬取 git log + 自动推断列 + CURATED 人工覆盖 + 生成 PRD/Excel）</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>新提交自动生成行；已知提交按 sha 覆盖</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:H19"/>
+  <autoFilter ref="A2:H21"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1349,8 +1349,92 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:10</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>C-020</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>变更追踪表收录独立主线的视觉重构提交（C-005）</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>generate_change_log.py 支持 EXTRA_SHAS + 按 subject 覆盖</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>9c2dd0e 强推覆盖后归位</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:36</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>C-021</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>合并视觉重构提交 9c2dd0e（A/B 测试通过）：新增 /contacts 通讯录页、agent-portrait 头像组件、恢复 software-dock；globals.css 视觉与响应式优化；设置页与 API Key/自定义模型功能共存</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>合并 settings-page.tsx（保留 API Key 管理 + 自定义模型功能并采用视觉样式）；新增 contacts 路由、agent-portrait.tsx、software-dock.tsx 恢复；agent-gallery/status-panel/app-sidebar/chat 视觉重构</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>仅 settings-page.tsx 1 处文本冲突手工合并；lint/test/build/pytest 全过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:H21"/>
+  <autoFilter ref="A2:H23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,17 +489,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -522,30 +523,35 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>Git 提交</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>改动类型</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>改动内容</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>前端技术</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>后端技术</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>是否有数据库</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -562,32 +568,37 @@
           <t>C-001</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>08ed038</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>全站优化：消除前端 4 处重复 WebSocket 逻辑与死代码，统一连接/任务工具/常量，增加 ErrorBoundary；后端事件契约规范化、记录模型成本、限制并发</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>提取共用 useWorkspaceSocket；删除死代码(SystemStatus/SoftwareDock/selectConsoleAgents)；新增 ErrorBoundary；常量集中 constants.ts；任务工具去重 task-utils.ts；fetchedRef 防护</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>TaskStepEventPayload Schema 替代手写 dict；LiteLLM 响应提取成本；并发控制(max 3, 429)；receipt 标注预留</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>前端测试 2→28；净减 237 行</t>
         </is>
@@ -604,32 +615,37 @@
           <t>C-002</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>8ab4834</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>README 更新本轮优化详情</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>README 章节补充</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>测试数 37/28</t>
         </is>
@@ -646,32 +662,37 @@
           <t>C-003</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>5f3b6a1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>README 全文中文化</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>README 全量翻译</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>全量翻译</t>
         </is>
@@ -688,32 +709,37 @@
           <t>C-004</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>3a99015</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>README 风格重写，加入架构图与关键决策记录</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>README 结构重排、徽章、ASCII 架构图</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>资深工程师口吻</t>
         </is>
@@ -730,32 +756,37 @@
           <t>C-005</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>9c2dd0e</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>前端视觉与响应式优化，新增通讯录 /contacts 页面与 Agent 头像组件</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>新增 agent-portrait.tsx、contacts-page.tsx(/contacts 路由)；agent-gallery/status-panel/app-sidebar/chat 组件重构；globals.css 视觉令牌与响应式优化</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>1203 插入/471 删除，21 文件；位于独立主线(原 main)，当前分支强推覆盖 origin/main 后未合入</t>
         </is>
@@ -772,32 +803,37 @@
           <t>C-006</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>19d4dca</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>是(provider_credentials)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Key 永不在列表回传</t>
         </is>
@@ -814,32 +850,37 @@
           <t>C-007</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>fb94fb2</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>新增 Windows 一键启动脚本</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>start.bat / start.ps1</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Docker Compose 封装；自动复制 .env + 等健康</t>
         </is>
@@ -856,32 +897,37 @@
           <t>C-008</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>f6ac2e8</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>仅生产 Docker 构建启用</t>
         </is>
@@ -898,32 +944,37 @@
           <t>C-009</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>48b3c47</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>新增自定义模型接入（任意 provider/model + fallback 降级）；修复 API Key 眼睛图标切换失效</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>自定义模型添加/删除 UI +「自定义」徽章；眼睛图标切换修复(undefined 与 React 批处理冲突)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>CustomModelConfig 模型；/api/custom-models；chat_completion 自定义解析；修按 name 查 PK bug</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>是(custom_model_configs)</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>后端 37→40</t>
         </is>
@@ -940,32 +991,37 @@
           <t>C-010</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>5b5e5d9</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>README 补充「模型与密钥管理」章节，更新测试数</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>README 章节补充</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>测试数 40/28</t>
         </is>
@@ -982,32 +1038,37 @@
           <t>C-011</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>4396cad</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>修复一键启动脚本中文乱码（UTF-8 被 cmd/PowerShell 按 ANSI 解析）</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>脚本消息改纯 ASCII</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>跨代码页安全</t>
         </is>
@@ -1024,32 +1085,37 @@
           <t>C-012</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>a138831</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>text-foreground 修复</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1066,32 +1132,37 @@
           <t>C-013</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>c8d1f72</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>设置页表单字段文字改纯白，提升可读性</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>text-white / white/90 / 占位符 white/40</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1108,32 +1179,37 @@
           <t>C-014</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>c374465</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>显式操作才返回 Key，列表仍不回传</t>
         </is>
@@ -1150,32 +1226,37 @@
           <t>C-015</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>abbb336</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>API Key 管理收敛为仅 DeepSeek 预设，用户可自行添加任意厂商的 API</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>「添加厂商」表单(任意厂商名+Key)；厂商名 title-case；移除其余预设</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>移除 Provider 白名单；/models/providers/status 只显示 deepseek+DB 厂商</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>否(复用 provider_credentials)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>后端 40→42</t>
         </is>
@@ -1192,32 +1273,37 @@
           <t>C-016</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>6289107</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>新增 docs/PRD.md 变更追踪表</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>表格 + 维护约定</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>建立本表，后续改动由脚本实时生成</t>
         </is>
@@ -1234,32 +1320,37 @@
           <t>C-017</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>fc35e0b</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>新增 Excel 变更追踪工作簿</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>openpyxl 生成脚本</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>表结构含颜色/冻结/筛选</t>
         </is>
@@ -1276,32 +1367,37 @@
           <t>C-018</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2ba41fc</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>变更追踪表新增「改动内容」列，明确记录每次改了什么</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>表结构更新(PRD.md + Excel)</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>业务描述与前后端技术分离</t>
         </is>
@@ -1318,32 +1414,37 @@
           <t>C-019</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>3049af9</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>变更追踪表改为从 git history 自动生成</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>generate_change_log.py（爬取 git log + 自动推断列 + CURATED 人工覆盖 + 生成 PRD/Excel）</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>新提交自动生成行；已知提交按 sha 覆盖</t>
         </is>
@@ -1360,32 +1461,37 @@
           <t>C-020</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>0bde63b</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>变更追踪表收录独立主线的视觉重构提交（C-005）</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>generate_change_log.py 支持 EXTRA_SHAS + 按 subject 覆盖</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>9c2dd0e 强推覆盖后归位</t>
         </is>
@@ -1402,41 +1508,93 @@
           <t>C-021</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>0c46b78</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>合并视觉重构提交 9c2dd0e（A/B 测试通过）：新增 /contacts 通讯录页、agent-portrait 头像组件、恢复 software-dock；globals.css 视觉与响应式优化；设置页与 API Key/自定义模型功能共存</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>合并 settings-page.tsx（保留 API Key 管理 + 自定义模型功能并采用视觉样式）；新增 contacts 路由、agent-portrait.tsx、software-dock.tsx 恢复；agent-gallery/status-panel/app-sidebar/chat 视觉重构</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>仅 settings-page.tsx 1 处文本冲突手工合并；lint/test/build/pytest 全过</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:38</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>C-022</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ffe1535</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>docs: record merge C-021 (visual aesthetics A/B test) in change log</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:H23"/>
+  <autoFilter ref="A2:I24"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,13 @@
     </font>
     <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -95,10 +102,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,11 +117,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -125,8 +134,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -489,18 +499,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -523,35 +538,60 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>Git 提交</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>改动类型</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>影响范围</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>改动内容</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>前端技术</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>后端技术</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>是否有数据库</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>破坏性变更</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>验证结果</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -570,37 +610,62 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>08ed038</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、前端</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>全站优化：消除前端 4 处重复 WebSocket 逻辑与死代码，统一连接/任务工具/常量，增加 ErrorBoundary；后端事件契约规范化、记录模型成本、限制并发</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>提取共用 useWorkspaceSocket；删除死代码(SystemStatus/SoftwareDock/selectConsoleAgents)；新增 ErrorBoundary；常量集中 constants.ts；任务工具去重 task-utils.ts；fetchedRef 防护</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>TaskStepEventPayload Schema 替代手写 dict；LiteLLM 响应提取成本；并发控制(max 3, 429)；receipt 标注预留</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>前端测试 2→28；净减 237 行</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>仅前端组件 + 后端工具函数改动，无外部 API 变化</t>
         </is>
       </c>
     </row>
@@ -617,35 +682,60 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>8ab4834</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>README 更新本轮优化详情</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>README 章节补充</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>测试数 37/28</t>
         </is>
@@ -664,35 +754,60 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>5f3b6a1</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>README 全文中文化</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>README 全量翻译</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>全量翻译</t>
         </is>
@@ -711,35 +826,60 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>3a99015</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>README 风格重写，加入架构图与关键决策记录</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>README 结构重排、徽章、ASCII 架构图</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>资深工程师口吻</t>
         </is>
@@ -758,37 +898,62 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>9c2dd0e</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>其他、配置、文档、前端</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>前端视觉与响应式优化，新增通讯录 /contacts 页面与 Agent 头像组件</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>新增 agent-portrait.tsx、contacts-page.tsx(/contacts 路由)；agent-gallery/status-panel/app-sidebar/chat 组件重构；globals.css 视觉令牌与响应式优化</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>1203 插入/471 删除，21 文件；位于独立主线(原 main)，当前分支强推覆盖 origin/main 后未合入</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>1203 插入/471 删除，21 文件；经 C-021 并入当前分支</t>
         </is>
       </c>
     </row>
@@ -805,37 +970,62 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>19d4dca</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、前端</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>新增「设置 → API Key 管理」：用户可在前端填入/删除各 Provider 密钥，存库优先于环境变量</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>设置页 API Key 管理 UI(密码框+眼睛+保存/删除)；use-settings 扩展</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>ProviderCredential 模型；GET/PUT/DELETE /api/provider-keys；Key 解析优先级 DB&gt;env</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>是(provider_credentials)</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Key 永不在列表回传</t>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>后端 37→40</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Key 永不在列表回传；新增表</t>
         </is>
       </c>
     </row>
@@ -852,35 +1042,60 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>fb94fb2</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>新增 Windows 一键启动脚本</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>start.bat / start.ps1</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Docker Compose 封装；自动复制 .env + 等健康</t>
         </is>
@@ -899,35 +1114,60 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>f6ac2e8</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>修复开发服务器端口无法访问（next.config standalone 配置与 dev 冲突）</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>output:standalone 改为 NEXT_BUILD_STANDALONE env 按需启用</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>build pass</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>仅生产 Docker 构建启用</t>
         </is>
@@ -946,37 +1186,62 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>48b3c47</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、前端</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>新增自定义模型接入（任意 provider/model + fallback 降级）；修复 API Key 眼睛图标切换失效</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>自定义模型添加/删除 UI +「自定义」徽章；眼睛图标切换修复(undefined 与 React 批处理冲突)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>CustomModelConfig 模型；/api/custom-models；chat_completion 自定义解析；修按 name 查 PK bug</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>是(custom_model_configs)</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>后端 37→40</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>新增表；含眼睛 BUG 修复</t>
         </is>
       </c>
     </row>
@@ -993,35 +1258,60 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>5b5e5d9</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>README 补充「模型与密钥管理」章节，更新测试数</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>README 章节补充</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>测试数 40/28</t>
         </is>
@@ -1040,35 +1330,60 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>4396cad</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>修复一键启动脚本中文乱码（UTF-8 被 cmd/PowerShell 按 ANSI 解析）</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>脚本消息改纯 ASCII</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>跨代码页安全</t>
         </is>
@@ -1087,35 +1402,60 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>a138831</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>修复设置页自定义模型表单 / API Key 输入框黑底黑字无法阅读</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>text-foreground 修复</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1134,35 +1474,60 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>c8d1f72</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>设置页表单字段文字改纯白，提升可读性</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>text-white / white/90 / 占位符 white/40</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1181,35 +1546,60 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>c374465</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>后端、前端</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>修复点击眼睛无法显示已保存 API Key（保存后清空 + Key 不回传，value 恒空）</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>眼睛点击时拉取真实 Key 填充输入框再切换可见性</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>新增 GET /api/provider-keys/{provider} 按需返回 Key；get_api_key_value()</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>后端 42 passed</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>显式操作才返回 Key，列表仍不回传</t>
         </is>
@@ -1228,37 +1618,62 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>abbb336</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>后端、前端</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>API Key 管理收敛为仅 DeepSeek 预设，用户可自行添加任意厂商的 API</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>「添加厂商」表单(任意厂商名+Key)；厂商名 title-case；移除其余预设</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>移除 Provider 白名单；/models/providers/status 只显示 deepseek+DB 厂商</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>否(复用 provider_credentials)</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>后端 40→42</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>API 行为变化：PUT 接受任意厂商名</t>
         </is>
       </c>
     </row>
@@ -1275,37 +1690,62 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>6289107</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>新增 docs/PRD.md 变更追踪表</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>表格 + 维护约定</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>建立本表，后续改动由脚本实时生成</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>建立本表，后续由脚本实时生成</t>
         </is>
       </c>
     </row>
@@ -1322,35 +1762,60 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>fc35e0b</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>新增 Excel 变更追踪工作簿</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>openpyxl 生成脚本</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>表结构含颜色/冻结/筛选</t>
         </is>
@@ -1369,35 +1834,60 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
           <t>2ba41fc</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>变更追踪表新增「改动内容」列，明确记录每次改了什么</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>表结构更新(PRD.md + Excel)</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>业务描述与前后端技术分离</t>
         </is>
@@ -1416,35 +1906,60 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>3049af9</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>变更追踪表改为从 git history 自动生成</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>generate_change_log.py（爬取 git log + 自动推断列 + CURATED 人工覆盖 + 生成 PRD/Excel）</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>新提交自动生成行；已知提交按 sha 覆盖</t>
         </is>
@@ -1463,35 +1978,60 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
           <t>0bde63b</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>变更追踪表收录独立主线的视觉重构提交（C-005）</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>generate_change_log.py 支持 EXTRA_SHAS + 按 subject 覆盖</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>9c2dd0e 强推覆盖后归位</t>
         </is>
@@ -1510,37 +2050,62 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
           <t>0c46b78</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>合并视觉重构提交 9c2dd0e（A/B 测试通过）：新增 /contacts 通讯录页、agent-portrait 头像组件、恢复 software-dock；globals.css 视觉与响应式优化；设置页与 API Key/自定义模型功能共存</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>合并 settings-page.tsx（保留 API Key 管理 + 自定义模型功能并采用视觉样式）；新增 contacts 路由、agent-portrait.tsx、software-dock.tsx 恢复；agent-gallery/status-panel/app-sidebar/chat 视觉重构</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>仅 settings-page.tsx 1 处文本冲突手工合并；lint/test/build/pytest 全过</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>lint/test/build/pytest 全过(42)</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>仅 settings-page.tsx 1 处文本冲突手工合并</t>
         </is>
       </c>
     </row>
@@ -1557,45 +2122,167 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
           <t>ffe1535</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>docs: record merge C-021 (visual aesthetics A/B test) in change log</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 15:06</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>C-023</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>d64090a</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>docs: add Git commit column to change log</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I24"/>
+  <autoFilter ref="A2:N25"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2253,8 +2253,152 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 15:09</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>C-024</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>08b8e10</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>docs: expand change log to professional 14-column layout</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:38</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>C-025</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>36854c8</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>为 Agent 增加工具调用（Function Calling）能力：chat_completion 支持 tools + tool_calls；新增工具注册表（calculate/query_tasks/get_agents/get_system_status）；orchestrator 工具循环（最大 5 轮）并持久化为 TaskStep；单 Agent 与 Worker 阶段启用</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>task-format.ts stepLabel 增加「工具调用」映射</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>litellm_service 支持 tools/tool_calls；新增 services/tools.py 注册表+安全计算；orchestrator 工具循环+TaskStep 持久化；config 新增 agent_tools_enabled</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>pytest 42→54；前端 28/build pass</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>详见 docs/prd/PRD-工具调用能力.md；不新增 WS 事件、不改表结构</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N25"/>
+  <autoFilter ref="A2:N27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2282,6 +2426,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>1203 插入/471 删除，21 文件；经 C-021 并入当前分支</t>
+          <t>1203 插入/471 删除，21 文件；经 C-021 并入当前分支；PRD: docs/prd/visual-aesthetics.md</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>Key 永不在列表回传；新增表</t>
+          <t>Key 永不在列表回传；新增表；PRD: docs/prd/api-key-management.md</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>Docker Compose 封装；自动复制 .env + 等健康</t>
+          <t>Docker Compose 封装；自动复制 .env + 等健康；PRD: docs/prd/launch-scripts.md</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>新增表；含眼睛 BUG 修复</t>
+          <t>新增表；含眼睛 BUG 修复；PRD: docs/prd/custom-models.md</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>API 行为变化：PUT 接受任意厂商名</t>
+          <t>API 行为变化：PUT 接受任意厂商名；PRD: docs/prd/api-key-management.md</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>仅 settings-page.tsx 1 处文本冲突手工合并</t>
+          <t>仅 settings-page.tsx 1 处文本冲突手工合并；PRD: docs/prd/visual-aesthetics.md</t>
         </is>
       </c>
     </row>
@@ -2397,8 +2397,224 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:39</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>C-026</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>e4c9e20</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>docs: register tool-calling requirement C-025 in change log</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:41</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>C-027</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>dab7448</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>为 5 个历史需求（Agent Console MVP / API Key 管理 / 自定义模型 / 前端视觉与响应式优化 / Windows 一键启动）补充详细 PRD 文档到 docs/prd/，并在追踪表对应行备注 PRD 链接</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>新增 docs/prd/agent-console-mvp.md、api-key-management.md、custom-models.md、visual-aesthetics.md、launch-scripts.md</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>generate_change_log.py CURATED 备注追加 PRD 链接</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>docs/PRD.md 增补「PRD 文档索引」；MVP 为基线前需求，以其 PRD 文档登记</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:43</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>C-028</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>958563f</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>docs: 登记 PRD 文档提交并加固变更追踪生成脚本</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N27"/>
+  <autoFilter ref="A2:N30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2428,6 +2644,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2472,7 +2472,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03 20:41</t>
+          <t>2026-08-03 20:54</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>dab7448</t>
+          <t>8716e45</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>文档</t>
+          <t>其他、文档</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2541,80 +2541,8 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 20:43</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>C-028</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>958563f</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>文档</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>docs: 登记 PRD 文档提交并加固变更追踪生成脚本</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:N30"/>
+  <autoFilter ref="A2:N29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2646,7 +2574,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2541,8 +2541,80 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:56</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>C-028</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>197f6e3</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>docs: 变更追踪表登记 PRD 文档提交</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N29"/>
+  <autoFilter ref="A2:N30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2574,6 +2646,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>1203 插入/471 删除，21 文件；经 C-021 并入当前分支；PRD: docs/prd/visual-aesthetics.md</t>
+          <t>1203 插入/471 删除，21 文件；经 C-021 并入当前分支；PRD: docs/prd/PRD-前端视觉与响应式优化.md</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>Key 永不在列表回传；新增表；PRD: docs/prd/api-key-management.md</t>
+          <t>Key 永不在列表回传；新增表；PRD: docs/prd/PRD-APIKey管理.md</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>Docker Compose 封装；自动复制 .env + 等健康；PRD: docs/prd/launch-scripts.md</t>
+          <t>Docker Compose 封装；自动复制 .env + 等健康；PRD: docs/prd/PRD-Windows一键启动脚本.md</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>新增表；含眼睛 BUG 修复；PRD: docs/prd/custom-models.md</t>
+          <t>新增表；含眼睛 BUG 修复；PRD: docs/prd/PRD-自定义模型接入.md</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>API 行为变化：PUT 接受任意厂商名；PRD: docs/prd/api-key-management.md</t>
+          <t>API 行为变化：PUT 接受任意厂商名；PRD: docs/prd/PRD-APIKey管理.md</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>仅 settings-page.tsx 1 处文本冲突手工合并；PRD: docs/prd/visual-aesthetics.md</t>
+          <t>仅 settings-page.tsx 1 处文本冲突手工合并；PRD: docs/prd/PRD-前端视觉与响应式优化.md</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>新增 docs/prd/agent-console-mvp.md、api-key-management.md、custom-models.md、visual-aesthetics.md、launch-scripts.md</t>
+          <t>新增 docs/prd/PRD-AgentConsoleMVP.md、PRD-APIKey管理.md、PRD-自定义模型接入.md、PRD-前端视觉与响应式优化.md、PRD-Windows一键启动脚本.md</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -2613,8 +2613,80 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 20:56</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>C-029</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>2313960</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>docs: 变更追踪表登记登记提交</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N30"/>
+  <autoFilter ref="A2:N31"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2647,6 +2719,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2685,8 +2685,80 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:04</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>C-030</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>c519372</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>docs: 统一 PRD 文档命名为 PRD-前缀</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N31"/>
+  <autoFilter ref="A2:N32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2720,6 +2792,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2688,77 +2688,221 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>2026-08-03 20:59</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>C-030</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>caaafe1</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>liwe123</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Add GitHub Actions workflow for Python package with Conda</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>2026-08-03 21:04</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>C-030</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>c519372</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>C-031</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>1fd9aba</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>其他、文档</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>docs: 统一 PRD 文档命名为 PRD-前缀</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:04</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>C-032</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>42dcda5</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>docs: 变更追踪表登记 PRD 重命名提交</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N32"/>
+  <autoFilter ref="A2:N34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2793,6 +2937,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2901,8 +2901,224 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 21:05</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>C-033</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>9d4a57e</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>docs: 变更追踪表登记 CI workflow 与 PRD 重命名提交</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:26</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>C-034</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>b7f7d27</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Sync optimized project into a clean Git baseline.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:28</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>C-035</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>29deb0e</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Merge remote history while preserving optimized project state.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N34"/>
+  <autoFilter ref="A2:N37"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -2939,6 +3155,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>Sync optimized project into a clean Git baseline.</t>
+          <t>同步优化版项目为新的 Git 基线</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>将优化后的完整项目作为当前主线基线提交</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Merge remote history while preserving optimized project state.</t>
+          <t>合并远端历史并保留当前优化版项目状态</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -3113,12 +3113,84 @@
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>采用 ours 策略合并远端历史后推送到 GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:34</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>C-036</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>6cab7da</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>同步优化版项目后刷新变更追踪表</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>更新 PRD 与 Excel 变更追踪表</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>生成脚本重跑</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>将新基线提交一并纳入改动表</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N37"/>
+  <autoFilter ref="A2:N38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3158,6 +3230,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3189,8 +3189,152 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:37</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>C-037</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>2d1e659</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>docs: make change log entries Chinese for recent sync</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:46</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>C-038</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>7039e2a</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>修复 GitHub Actions Python 包工作流以运行后端测试</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>backend/requirements-dev.txt；backend/tests；.github/workflows/python-package-conda.yml</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>backend/tests/test_health.py 通过</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>移除缺失的 environment.yml 依赖，改为 pip 安装并在 backend 目录执行 pytest</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N38"/>
+  <autoFilter ref="A2:N40"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3231,6 +3375,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3333,8 +3333,80 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:49</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>C-039</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>0e0a15f</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>docs: record the GitHub Actions workflow fix in the change log</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N40"/>
+  <autoFilter ref="A2:N41"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3377,6 +3449,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3405,8 +3405,224 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:42</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>C-040</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>c190d7d</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、其他、文档</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>fix: harden provider lookup and task recovery</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/api；backend/app/core；backend/app/db；backend/app/models；backend/app/schemas；backend/app/services；backend/tests/test_api.py；backend/tests/test_task_recovery.py；backend/tests/test_tools.py</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>是(task)</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:54</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>C-041</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>c36bf54</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>fix: update database schema test for task lease fields</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>backend/tests/test_database.py</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>C-042</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>前端交互体验完善：Software Dock 状态详情、移动端快捷指令、安全 Markdown；修复主题冲突、通讯录搜索分组、动态提及与 Agent 弹窗无障碍问题</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>globals.css 统一深色主题；chat composer 动态 Agent/移动快捷操作；message bubble 安全 Markdown；Agent Dialog 焦点与键盘支持；Dock 可交互；通讯录和设置表单优化</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-前端交互体验完善.md；分类包含 Requirement、BUG、Optimization</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N41"/>
+  <autoFilter ref="A2:N44"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3450,6 +3666,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>前端交互体验完善：Software Dock 状态详情、移动端快捷指令、安全 Markdown；修复主题冲突、通讯录搜索分组、动态提及与 Agent 弹窗无障碍问题</t>
+          <t>Software Dock 增加可操作的连接状态详情</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>globals.css 统一深色主题；chat composer 动态 Agent/移动快捷操作；message bubble 安全 Markdown；Agent Dialog 焦点与键盘支持；Dock 可交互；通讯录和设置表单优化</t>
+          <t>software-dock.tsx：展示软件名称、接入位、在线状态；支持鼠标与键盘操作</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -3617,12 +3617,1020 @@
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>PRD: docs/prd/PRD-前端交互体验完善.md；分类包含 Requirement、BUG、Optimization</t>
+          <t>PRD FR1；依赖同提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>C-043</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Agent 消息支持安全 Markdown 结构化渲染</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>message-bubble.tsx + react-markdown：标题、列表、行内代码、代码块、安全外链；跳过原始 HTML</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>PRD FR2；package.json/package-lock.json 新增 react-markdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>C-044</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>移动端聊天增加快捷指令与 Agent 选择面板</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>chat-composer.tsx：移动快捷操作入口、模板列表、动态 Agent 列表</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>PRD FR3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>C-045</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Agent 详情弹层补齐完整交互能力</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>agent-gallery.tsx：Dialog 语义、Escape/遮罩关闭、背景滚动锁定、焦点恢复</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>PRD FR4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>C-046</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>修复移动端浅色变量与根节点深色主题冲突</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>globals.css：移除按屏幕宽度覆盖主题色与 color-scheme 的规则</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>C-047</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>修复通讯录搜索后 Agent 服务分组错乱</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>contacts-page.tsx：先按原始服务归属分组，再分别执行搜索过滤</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>C-048</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>修复通讯录在线人数与连接状态不一致</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>contacts-page.tsx：结合 WebSocket 连接状态与 Agent 状态计算在线人数</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>C-049</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>修复聊天提及列表依赖固定中文姓名</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>chat-composer.tsx：基于接口 Agent 数据和角色优先级生成提及列表</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>C-050</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>修复客户端 mention 查询参数变化后输入框不更新</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>chat-composer.tsx：监听查询参数并去重追加提及，保留用户已有输入</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>C-051</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>设置页表单统一使用全局语义颜色</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>settings-page.tsx：输入框改用 background/foreground/input/muted 设计令牌</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>C-052</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Agent 卡片扩大为完整语义化交互区域</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>agent-gallery.tsx：头像、姓名、状态和角色合并为可聚焦按钮</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>C-053</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>完善通讯录搜索范围、无结果状态与清空操作</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>contacts-page.tsx：支持姓名/角色/职责，Escape 清空，无结果提示与清空按钮</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>C-054</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>提升 Agent 角色辅助文字可读性</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>agent-gallery.tsx：角色文字由 10px 调整为 11px</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:40</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>C-055</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>53268f4</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>其他、前端</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>新增前端交互体验完善 PRD</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>docs/prd/PRD-前端交互体验完善.md</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码与视觉对比通过；375/桌面冒烟通过；lint + 28 tests + build 通过</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>登记 Requirement 的目标、用户故事、FR 与验收标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:43</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>C-056</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>39dae3c</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>docs: register frontend experience changes</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N44"/>
+  <autoFilter ref="A2:N58"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3669,6 +4677,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4629,8 +4629,1016 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:52</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>C-057</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>6816c87</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>docs: itemize every frontend change in tracking table</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>C-058</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>新增可选 API Token 访问控制</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>APP_API_TOKEN；REST 支持 Bearer/X-API-Key；WebSocket 支持请求头或 token 查询参数</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-后端访问控制与工作区隔离.md；FR1-FR3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>C-059</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Agent 工具继承可信工作区执行上下文</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Orchestrator 注入 workspace_id；query_tasks/get_agents 强制按当前工作区过滤并忽略模型伪造范围</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>PRD FR4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>C-060</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Provider Key 接口改为仅返回掩码元数据</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>设置页查看已保存凭证时仅显示掩码，并禁止将掩码作为新密钥保存</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>ProviderKeyValue 返回 configured/masked_key/source，不再返回 api_key 原文</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>PRD FR5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>C-061</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>修复客户端可伪造 Agent/System 消息</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>公开消息接口仅接受 user + normal，拒绝 sender_id、Agent、System 与其他消息类型</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>C-062</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>修复客户端可篡改任务执行状态与租约</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>TaskCreate/TaskUpdate 移除 status/result/execution_token/expires_at 等服务端字段</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>C-063</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>修复工作区活跃任务配额漏算 Pending 任务</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>MessageHub 配额统计改为 Pending + Running，达到上限返回 429</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>C-064</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>修复重启恢复任务绕过工作区并发额度</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>recover_unfinished_tasks 按 Workspace 计算可用额度并限量调度</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>C-065</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>修复长任务固定租约过期后可能被重复执行</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Orchestrator 启动后台 lease heartbeat，按 execution_token 条件定期续租并在结束时取消</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>C-066</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>修复模型测试接口无法识别数据库自定义模型</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>models/test 同时传入 DB API Keys 与 DB custom_models</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>C-067</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>修复模型列表忽略数据库 Provider Key 状态</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>models 列表统一以 DB 优先、环境变量兜底判断 configured</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>C-068</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>修复删除仍被引用的自定义模型导致悬空配置</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>删除前检查 Agent.model_name 和其他模型 fallback_model，存在引用返回 409</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>C-069</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>补充后端访问控制与工作区隔离回归测试</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>新增 API Token、消息伪造、任务字段保护、凭证脱敏、工具跨工作区隔离测试；更新既有 API 契约测试</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>无需 PRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:20</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>C-070</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>71ea26f</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>新增后端访问控制与工作区隔离 PRD</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>docs/prd/PRD-后端访问控制与工作区隔离.md</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>是（消息、任务更新、Provider Key GET 响应契约收紧）</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>A/B 代码对比通过；API 冒烟通过；56 tests + compileall + pip check 通过</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>覆盖目标、FR、非功能需求与验收标准</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N58"/>
+  <autoFilter ref="A2:N72"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -4691,6 +5699,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5637,8 +5637,296 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:23</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>C-071</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>555c064</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>docs: register backend hardening changes</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-09 20:04</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>C-072</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>51bf567</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>docs: add architecture and task flow diagrams</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:09</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>C-073</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>70e53ee</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>后端、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>add task-level context continuity tracing</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>frontend/src/components；frontend/src/types</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/agents；backend/app/api；backend/app/core；backend/app/schemas；backend/tests/test_api.py；backend/tests/test_orchestrator.py；backend/tests/test_tools.py</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-09 22:30</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C-074</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>70e53ee</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>????????????????????????????????????????????????????????????</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>backend/app/core/orchestrator.py?backend/app/core/execution_trace.py?backend/app/agents/manager_agent.py?backend/app/agents/worker_agent.py?backend/app/agents/final_agent.py?backend/tests/test_orchestrator.py?backend/tests/test_tools.py?frontend/src/components/tasks/task-detail-page.tsx?frontend/src/hooks/use-tasks.ts?frontend/src/types/task.ts</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>backend/app/api/v1/endpoints/tasks.py?backend/app/schemas/task.py?backend/app/core/orchestrator.py?backend/app/core/execution_trace.py?backend/tests/test_api.py?backend/tests/test_orchestrator.py?backend/tests/test_tools.py</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>A/B ???????API/Orchestrator/Tools ???????pytest tests/test_api.py tests/test_orchestrator.py tests/test_tools.py??36 tests pass?4 ?????????????</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-????????????????.md??????????????</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N72"/>
+  <autoFilter ref="A2:N75"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -5713,6 +6001,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5807,9 +5807,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -5819,22 +5819,22 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>add task-level context continuity tracing</t>
+          <t>单任务上下文连续性保障（上游抽象设计）：任务级上下文构建器 + 模型调用前结构化上下文回灌 + 工具结果/失败信息稳定继承 + 多 Agent 阶段共享 + 失败重试可读历史 + 超长摘要裁剪</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>frontend/src/components；frontend/src/types</t>
+          <t>任务详情页「任务上下文」模块（当前阶段/摘要/工具链/失败与恢复记录）</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>backend/app/agents；backend/app/api；backend/app/core；backend/app/schemas；backend/tests/test_api.py；backend/tests/test_orchestrator.py；backend/tests/test_tools.py</t>
+          <t>orchestrator.py 各阶段注入 build_context_message；execution_trace.py 上下文构建与摘要裁剪；schemas/task.py 上下文/轨迹字段</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>否（复用 Task/TaskStep/ModelCall 拼装，未新增表）</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -5844,89 +5844,89 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>后端 build/测试通过；前端 build pass</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>详见 docs/prd/PRD-单任务上下文连续性与执行过程可视化.md（2026-08-10 由两份 PRD 合并而来）；与 8e22c25 为同一能力的抽象层与实现层</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-08-09 22:30</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-09 23:08</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>C-074</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>70e53ee</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>8e22c25</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>????????</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>????????????????????????????????????????????????????????????</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>backend/app/core/orchestrator.py?backend/app/core/execution_trace.py?backend/app/agents/manager_agent.py?backend/app/agents/worker_agent.py?backend/app/agents/final_agent.py?backend/tests/test_orchestrator.py?backend/tests/test_tools.py?frontend/src/components/tasks/task-detail-page.tsx?frontend/src/hooks/use-tasks.ts?frontend/src/types/task.ts</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>backend/app/api/v1/endpoints/tasks.py?backend/app/schemas/task.py?backend/app/core/orchestrator.py?backend/app/core/execution_trace.py?backend/tests/test_api.py?backend/tests/test_orchestrator.py?backend/tests/test_tools.py</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>A/B ???????API/Orchestrator/Tools ???????pytest tests/test_api.py tests/test_orchestrator.py tests/test_tools.py??36 tests pass?4 ?????????????</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>PRD: docs/prd/PRD-????????????????.md??????????????</t>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、文档</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>任务执行过程可视化与工具调用追踪：新增执行轨迹层，模型每次继续执行前回灌结构化上下文（任务摘要/当前阶段/已完成步骤/工具结果/失败原因）；工具调用形成显式可回放链路；上下文过长时摘要裁剪；失败/重试可读取历史轨迹续跑</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>task-detail-page.tsx 新增 ExecutionTracePanel（轨迹摘要卡 + 执行轨迹时间线渲染）；types/task.ts 定义 TaskTraceEvent</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>新增 core/execution_trace.py（TraceArtifact/build_context_message/build_execution_trace/build_trace_artifact，含上下文构建+工具链路提取+两级摘要裁剪+脱敏）；orchestrator.py 模型调用前注入 build_context_message、阶段推进写入轨迹；schemas/task.py 增 TaskTraceRead/TaskDetailRead 轨迹字段；tasks.py _task_detail 实时组装 trace；前端 HTTP 轮询实现实时刷新</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>否（复用 Task/TaskStep/ModelCall 拼装，未新增表）</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>后端 build/测试通过；前端 build pass；任务详情页轨迹视图与工具链路可正常展示</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>详见 docs/prd/PRD-单任务上下文连续性与执行过程可视化.md（2026-08-10 由两份 PRD 合并而来）；FR8 WebSocket 推送、FR9 双层视图暂未落地（P1 级），AC6 由 HTTP 轮询达成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N75"/>
+  <autoFilter ref="A2:N76"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6004,6 +6004,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,7 +101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,9 +123,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -499,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -695,9 +687,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -767,9 +759,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -839,9 +831,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -911,7 +903,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -983,7 +975,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -1055,7 +1047,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -1127,7 +1119,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -1199,7 +1191,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -1271,9 +1263,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1343,7 +1335,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -1415,7 +1407,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -1487,7 +1479,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -1559,7 +1551,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -1631,7 +1623,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -1703,9 +1695,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1775,9 +1767,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1847,9 +1839,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1919,9 +1911,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1991,9 +1983,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2063,7 +2055,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -2135,9 +2127,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2207,9 +2199,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2279,9 +2271,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2351,7 +2343,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -2423,9 +2415,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2497,7 +2489,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2567,9 +2559,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2639,9 +2631,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2711,9 +2703,9 @@
           <t>liwe123</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2783,9 +2775,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2855,9 +2847,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2927,9 +2919,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2999,9 +2991,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -3071,9 +3063,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3143,9 +3135,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -3215,9 +3207,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3287,9 +3279,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3359,9 +3351,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3431,7 +3423,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -3503,7 +3495,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -3575,7 +3567,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -3647,7 +3639,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -3719,7 +3711,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -3791,7 +3783,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -3863,7 +3855,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -3935,7 +3927,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -4007,7 +3999,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -4079,7 +4071,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -4151,7 +4143,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -4513,7 +4505,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -4583,9 +4575,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -4655,9 +4647,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -4727,7 +4719,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -4799,7 +4791,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -4871,7 +4863,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
@@ -4943,7 +4935,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5015,7 +5007,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5087,7 +5079,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5159,7 +5151,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5231,7 +5223,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5303,7 +5295,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5375,7 +5367,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5447,7 +5439,7 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>BUG</t>
         </is>
@@ -5593,7 +5585,7 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -5663,9 +5655,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -5712,7 +5704,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 20:04</t>
+          <t>2026-08-07 22:47</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5727,7 +5719,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>51bf567</t>
+          <t>6622d08</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -5735,19 +5727,19 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>文档</t>
+          <t>其他、文档</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>docs: add architecture and task flow diagrams</t>
+          <t xml:space="preserve"> docs: organize consolidated PRD documentation</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -5784,7 +5776,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 21:09</t>
+          <t>2026-08-07 22:56</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5799,7 +5791,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>70e53ee</t>
+          <t>352503e</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -5809,124 +5801,340 @@
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>BUG</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>后端、文档、其他、前端</t>
+          <t>其他、文档</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>单任务上下文连续性保障（上游抽象设计）：任务级上下文构建器 + 模型调用前结构化上下文回灌 + 工具结果/失败信息稳定继承 + 多 Agent 阶段共享 + 失败重试可读历史 + 超长摘要裁剪</t>
+          <t>docs: 修复 PRD.html 目录扁平化与标题层级</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>任务详情页「任务上下文」模块（当前阶段/摘要/工具链/失败与恢复记录）</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>orchestrator.py 各阶段注入 build_context_message；execution_trace.py 上下文构建与摘要裁剪；schemas/task.py 上下文/轨迹字段</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>否（复用 Task/TaskStep/ModelCall 拼装，未新增表）</t>
+          <t>否</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>后端 build/测试通过；前端 build pass</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t>详见 docs/prd/PRD-单任务上下文连续性与执行过程可视化.md（2026-08-10 由两份 PRD 合并而来）；与 8e22c25 为同一能力的抽象层与实现层</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
+          <t>2026-08-09 20:04</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>C-074</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>51bf567</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>docs: add architecture and task flow diagrams</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:09</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>C-075</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>70e53ee</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>后端、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>单任务上下文连续性保障（上游抽象设计）：任务级上下文构建器 + 模型调用前结构化上下文回灌 + 工具结果/失败信息稳定继承 + 多 Agent 阶段共享 + 失败重试可读历史 + 超长摘要裁剪</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>任务详情页「任务上下文」模块（当前阶段/摘要/工具链/失败与恢复记录）</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>orchestrator.py 各阶段注入 build_context_message；execution_trace.py 上下文构建与摘要裁剪；schemas/task.py 上下文/轨迹字段</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>否（复用 Task/TaskStep/ModelCall 拼装，未新增表）</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>后端 build/测试通过；前端 build pass</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>详见 docs/prd/PRD-单任务上下文连续性与执行过程可视化.md（2026-08-10 由两份 PRD 合并而来）；与 8e22c25 为同一能力的抽象层与实现层</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
           <t>2026-08-09 23:08</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>C-074</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>C-076</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>8e22c25</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>后端、其他、文档</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>任务执行过程可视化与工具调用追踪：新增执行轨迹层，模型每次继续执行前回灌结构化上下文（任务摘要/当前阶段/已完成步骤/工具结果/失败原因）；工具调用形成显式可回放链路；上下文过长时摘要裁剪；失败/重试可读取历史轨迹续跑</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>task-detail-page.tsx 新增 ExecutionTracePanel（轨迹摘要卡 + 执行轨迹时间线渲染）；types/task.ts 定义 TaskTraceEvent</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>新增 core/execution_trace.py（TraceArtifact/build_context_message/build_execution_trace/build_trace_artifact，含上下文构建+工具链路提取+两级摘要裁剪+脱敏）；orchestrator.py 模型调用前注入 build_context_message、阶段推进写入轨迹；schemas/task.py 增 TaskTraceRead/TaskDetailRead 轨迹字段；tasks.py _task_detail 实时组装 trace；前端 HTTP 轮询实现实时刷新</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>否（复用 Task/TaskStep/ModelCall 拼装，未新增表）</t>
         </is>
       </c>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>后端 build/测试通过；前端 build pass；任务详情页轨迹视图与工具链路可正常展示</t>
         </is>
       </c>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="N78" s="5" t="inlineStr">
         <is>
           <t>详见 docs/prd/PRD-单任务上下文连续性与执行过程可视化.md（2026-08-10 由两份 PRD 合并而来）；FR8 WebSocket 推送、FR9 双层视图暂未落地（P1 级），AC6 由 HTTP 轮询达成</t>
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:58</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>C-077</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>f8a84b7</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>合并两份重叠 PRD（单任务上下文连续性保障 70e53ee/C-075 与 任务执行过程可视化与工具调用追踪 8e22c25/C-076）为统一版 PRD-单任务上下文连续性与执行过程可视化.md：背景缺口合并为 4 项、核心概念整合 5 个、FR 统一为 10 条、数据模型决策与实施状态（FR1-FR7/FR10 已落地，FR8/FR9 未落地）写入文档</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>docs/prd/ 目录 10→9 份（删除 2 份旧 PRD，新增 1 份合并版）；docs/PRD.md 索引同步 10→9 行</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>generate_change_log.py：补登记 70e53ee（C-075 升级为完整 Requirement）、C-075/C-076 备注指向合并版、is_excluded 改为 all() 语义（仅纯生成物提交跳过，合并提交保留）</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>重跑生成脚本 77 行；Excel 无乱码；HTML 阅读器 9 PRDs</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>合并版含 §8.4 决策记录与 §16 实施状态章节；两份旧 PRD 可从 git 历史找回</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N76"/>
+  <autoFilter ref="A2:N79"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6005,6 +6213,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEBEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,6 +128,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6133,8 +6141,80 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:28</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>C-078</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>f727400</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>docs: add Agent 任务守则 and sync change types (Docs-&gt;Requirement/Bug/Optimization)</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N79"/>
+  <autoFilter ref="A2:N80"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6216,6 +6296,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6159,62 +6159,134 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
+          <t>580daad</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>docs: regenerate change log and PRD.html (register Agent 任务守则 as C-078)</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:28</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>C-079</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
           <t>f727400</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t>Docs</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>其他、文档</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>docs: add Agent 任务守则 and sync change types (Docs-&gt;Requirement/Bug/Optimization)</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N80"/>
+  <autoFilter ref="A2:N81"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6297,6 +6369,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6285,8 +6285,80 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>C-080</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>897704c</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>docs: refine Agent 任务守则 (commit convention, CURATED workflow, test cmds, acceptance closure)</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N81"/>
+  <autoFilter ref="A2:N82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6370,6 +6442,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEBEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,9 +123,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -499,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6167,9 +6159,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -6239,9 +6231,9 @@
           <t>LI</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>Docs</t>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -6303,62 +6295,566 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
+          <t>0e3e1de</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>docs: regenerate change log (register 守则 refinement as C-080)</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:38</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>C-081</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
           <t>897704c</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>其他、文档</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>docs: refine Agent 任务守则 (commit convention, CURATED workflow, test cmds, acceptance closure)</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:33</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>C-082</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>0c46dd7</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>其他、部署</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>fix(deploy): wire APP_API_TOKEN and AGENT_TOOLS_ENABLED through docker-compose/.env</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:33</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>C-083</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>19e6eae</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>optimize: exclude .workbuddy and backup xlsx from git</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:33</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>C-084</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>5121ce1</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>docs: fix README inconsistencies and add code review report</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:33</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>C-085</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>55a8b1c</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>optimize(governance): drop illegal Docs enum from change log generator and PRD</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:33</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>C-086</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>69095e2</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>fix(scripts): correct start.ps1 health-check wait loop</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:33</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>C-087</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>c0d1cd2</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>fix(security): guard safe_eval against exponent DoS</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/services</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N82"/>
+  <autoFilter ref="A2:N89"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6443,6 +6939,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6853,8 +6853,80 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:34</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>C-088</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>398904e</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>docs: regenerate change log (register review fixes as C-082..C-087)</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N89"/>
+  <autoFilter ref="A2:N90"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -6946,6 +7018,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N90"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>docs: record merge C-021 (visual aesthetics A/B test) in change log</t>
+          <t>将视觉重构提交 C-021（A/B 测试通过）登记进变更追踪表</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>docs: add Git commit column to change log</t>
+          <t>变更追踪表新增「Git 提交」列，记录每次改动对应的提交哈希</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>docs: expand change log to professional 14-column layout</t>
+          <t>变更追踪表扩展为专业 14 列布局（含状态/类型/影响范围/前后端技术/数据库/破坏性变更等）</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>docs: register tool-calling requirement C-025 in change log</t>
+          <t>将工具调用能力需求 C-025 登记进变更追踪表</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Add GitHub Actions workflow for Python package with Conda</t>
+          <t>新增 GitHub Actions 工作流（Python 包 + Conda 环境）用于后端测试</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>docs: make change log entries Chinese for recent sync</t>
+          <t>将近期同步相关的变更表条目改为中文描述</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>docs: record the GitHub Actions workflow fix in the change log</t>
+          <t>将 GitHub Actions 工作流修复登记进变更追踪表</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>fix: harden provider lookup and task recovery</t>
+          <t>修复 Provider 查询与任务恢复逻辑的健壮性问题</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>fix: update database schema test for task lease fields</t>
+          <t>更新数据库 schema 测试以覆盖任务租约字段</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>docs: register frontend experience changes</t>
+          <t>将前端交互体验改动登记进变更追踪表</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>docs: itemize every frontend change in tracking table</t>
+          <t>将每一项前端改动逐条拆登记进变更追踪表</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>docs: register backend hardening changes</t>
+          <t>将后端访问控制加固改动登记进变更追踪表</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> docs: organize consolidated PRD documentation</t>
+          <t>整理合并版 PRD 文档（统一多份需求文档结构）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>docs: add architecture and task flow diagrams</t>
+          <t>新增架构图与任务流转图到 PRD 文档</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>fix(deploy): wire APP_API_TOKEN and AGENT_TOOLS_ENABLED through docker-compose/.env</t>
+          <t>修复部署配置：在 docker-compose/.env 透传 APP_API_TOKEN 与 AGENT_TOOLS_ENABLED，使容器内鉴权可用</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>optimize: exclude .workbuddy and backup xlsx from git</t>
+          <t>优化：在 .gitignore 排除 .workbuddy/ 与备份 xlsx，机械落实守则④排除项</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>docs: fix README inconsistencies and add code review report</t>
+          <t>文档：修正 README 两处不一致（SoftwareDock 保留面板、/contacts 已实现），新增代码审查报告</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>optimize(governance): drop illegal Docs enum from change log generator and PRD</t>
+          <t>治理优化：从变更表生成器与 PRD 中移除非法的第 4 枚举 Docs，仅保留 Requirement/Optimization/BUG</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>fix(scripts): correct start.ps1 health-check wait loop</t>
+          <t>修复脚本：修正 start.ps1 健康检查等待循环（until($?) 首轮恒真导致死循环）</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>fix(security): guard safe_eval against exponent DoS</t>
+          <t>安全修复：safe_eval 增加指数 DoS 防护，限制常量指数 ≤64，拦截 9**9**9 类爆炸输入</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>docs: regenerate change log (register review fixes as C-082..C-087)</t>
+          <t>文档：重跑生成脚本，将本轮审查修复登记为 C-082~C-087，变更表无 Docs 残留</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
@@ -6925,8 +6925,80 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:38</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>C-089</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>a3377e6</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>治理优化：清除变更表生成脚本内残留的 Docs 字面量（源侧与输出一致），并重跑生成脚本同步 PRD/xlsx</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N90"/>
+  <autoFilter ref="A2:N91"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7019,6 +7091,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6997,8 +6997,152 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:53</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>C-090</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>d41840a</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>文档：将变更追踪表全部改动内容中文化，消除英文 git 主题 fallback；重跑生成脚本同步 PRD/xlsx</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>generate_change_log.py 新增 _CONTENT_FIXES_BY_SHA（21 行 sha→中文内容）</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>重跑后改动内容列零英文</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>守则① 改动内容中文化；regen 提交自身行由本 subject 登记保持中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:50</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>C-091</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>d88bc6a</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>docs: update README to reflect latest architecture and multi-agent pipeline</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N91"/>
+  <autoFilter ref="A2:N93"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7092,6 +7236,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N93"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7141,8 +7141,80 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:03</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>C-092</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>c6c8041</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档、前端</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>optimize: 前端页面整体风格全面升级为 Google Pixel (Material You / M3) 设计风格</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>frontend/src/app；frontend/src/components</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N93"/>
+  <autoFilter ref="A2:N94"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7238,6 +7310,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7159,62 +7159,278 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
+          <t>b91c5ed</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 Google Pixel 风格优化至变更追踪表与 PRD.html</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:03</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>C-093</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
           <t>c6c8041</t>
         </is>
       </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>LI</t>
-        </is>
-      </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>其他、文档、前端</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>optimize: 前端页面整体风格全面升级为 Google Pixel (Material You / M3) 设计风格</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>frontend/src/app；frontend/src/components</t>
         </is>
       </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:31</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>C-094</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>4fc3875</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>docs: refine README formatting and links</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:07</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>C-095</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>f4ec8c8</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>完成项目 Phase 0 架构盘点，统一记录当前模块职责、任务主链路、任务状态机、Trace/Correlation 标识规范、风险清单与演进边界，为后续 PostgreSQL、TaskService、Worker 和事件总线改造提供约束基线</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>docs/架构治理基线.md；基于 MessageHub、AgentOrchestrator、任务租约、启动恢复和 WebSocket 当前实现形成架构基线</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>A/B 文档覆盖对比通过（改前无 Phase 0 基线，改后覆盖 6 类交付物）；文档冒烟通过；后端 56 tests passed</t>
+        </is>
+      </c>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>任务类型为 Optimization，无需新增 PRD；独立验收通过；生成脚本与 PRD.html 已重跑对齐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N94"/>
+  <autoFilter ref="A2:N97"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7311,6 +7527,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7429,8 +7429,152 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:08</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>C-096</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>d3f256f</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 Phase 0 变更追踪与 PRD 阅读器</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:35</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>C-097</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>2ada67f</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、数据库</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>新增持久化任务队列与独立 Worker，将消息接入和任务执行解耦，并提供优先级、执行租约、失败重试、超时回收、死信和并发控制能力</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>新增 TaskQueueItem、TaskService 与独立 Worker；MessageHub 统一入队；支持 inline/worker 两种执行模式</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>是(task_queue_items)</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>否（默认保持 inline 模式兼容）</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>A/B 执行模式对比通过；后端 59 tests passed；启动模式与队列复验 8 passed；git diff --check 通过</t>
+        </is>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-Phase2持久化任务队列与独立Worker.md；独立只读验收通过；生成脚本与 PRD.html 已重跑对齐</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N97"/>
+  <autoFilter ref="A2:N99"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7530,6 +7674,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7573,8 +7573,80 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:38</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>C-098</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>051860e</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 Phase 2 变更追踪与 PRD 阅读器</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N99"/>
+  <autoFilter ref="A2:N100"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7676,6 +7748,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7645,8 +7645,80 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:38</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>C-099</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>1b59316</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>docs: 登记 Phase 2 文档同步提交</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N100"/>
+  <autoFilter ref="A2:N101"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7749,6 +7821,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7717,8 +7717,152 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 12:29</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>C-100</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>38f9cbb</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、文档</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>feat: Phase 3 分布式化——事件总线、连接解耦、Worker注册中心与状态快照</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/core；backend/app/main.py；backend/app/websocket；backend/tests/test_distributed_event_bus.py；backend/tests/test_event_relay.py；backend/tests/test_worker_registry.py</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 22:41</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>C-101</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>9337826</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>新增用户认证系统（A1）：引入 User 数据模型与 PBKDF2/JWT 认证，提供注册、登录、Token 刷新、登出与当前用户信息接口；支持 API Token 与 JWT 双轨鉴权；WebSocket 握手 JWT 鉴权；前端新增登录页、注册页、客户端路由守卫与 API 客户端 401 自动续期</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>新增 /login 与 /register 登录注册页面；新增 AuthGuard 客户端路由守卫；task-api.ts 支持 Bearer Token 自动注入与 401 无感刷新；WebSocket 连接携带 JWT</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>新增 User 数据库模型；新增 auth.py 模块(JWT 签发/校验与密码哈希)；新增 /api/v1/auth 路由(register/login/refresh/logout/me)；main.py 中间件双轨鉴权</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>是(users)</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>否（保持与现有 API Token 向后兼容）</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>前后端冒烟测试通过；后端全量 99 passed；前端测试 28 passed；前端 lint/build 均通过</t>
+        </is>
+      </c>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-用户认证系统.md；工单 C-101；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N101"/>
+  <autoFilter ref="A2:N103"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7822,6 +7966,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7861,8 +7861,152 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 22:43</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>C-102</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>702942c</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 A1 用户认证系统变更追踪表、PRD 索引与接力文档</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 22:53</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>C-103</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>ad18c19</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>新增 RBAC 角色权限模型与多租户 Workspace 隔离（A2+A3）：引入 workspace_memberships 与 workspace_invitations 表；实现四级角色（owner/admin/member/viewer）与权限矩阵；提供工作区创建、我的工作区、成员列表、邀请码生成与加入等 API；前端实现侧边栏工作区切换器、成员管理台（/settings/members）与用户退出登录</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>新增 useWorkspaces 与 usePermissions hooks；AppSidebar 新增工作区切换器浮层、创建/加入弹窗与退出登录；新增 /settings/members 成员管理台；设置中心增加成员管理入口</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>新增 WorkspaceMembership 与 WorkspaceInvitation 模型；新增 core/permissions.py 权限矩阵与拦截依赖；新增 endpoints/workspace_members.py；注册自动建立工作区关系</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>是(workspace_memberships, workspace_invitations)</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>pytest 全量 100 passed；前端测试 28 passed；前端 lint/build 均通过；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-角色权限与多租户隔离.md；工单 C-103；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N103"/>
+  <autoFilter ref="A2:N105"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -7968,6 +8112,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8005,8 +8005,152 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 22:54</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>C-104</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>22208c7</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 RBAC 与多租户隔离变更追踪表、PRD 索引与接力文档</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:03</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>C-105</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>1ca7aec</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>新增平台级审计日志（B1）与成本统计面板（C1）：引入 audit_logs 表与审计服务，在登录、注册、成员变更与任务中自动埋点；实现成本中心多维聚合统计（总览指标/每日趋势/模型分布/Top任务）；前端实现 /settings/audit 审计日志台与 /settings/cost 成本统计大屏</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>新增 /settings/audit 审计操作日志控制台与 /settings/cost 成本中心与 Token 分析大屏；设置中心首页增加审计与成本快捷导航卡片</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>新增 AuditLog 模型；新增 audit_service.py 异步记录器；新增 endpoints/audit_logs.py 与 endpoints/cost_stats.py 并挂载路由与 RBAC 权限拦截；auth/members/tasks 自动埋点</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>是(audit_logs)</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>pytest 全量 102 passed；前端测试 28 passed；前端 lint/build 0 errors 0 warnings 通过；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-平台级审计日志.md, docs/prd/PRD-成本统计面板.md；工单 C-105, C-106；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N105"/>
+  <autoFilter ref="A2:N107"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8114,6 +8258,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N107"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8149,8 +8149,152 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:04</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>C-106</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>6019883</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步平台审计日志与成本统计变更追踪表、PRD 索引与接力文档</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:12</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>C-107</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>a4c0c1f</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>实现任务执行回放与单步调试（B2）及工作区配额治理（C2）：引入 quota_configs 表与配额限流服务；实现任务结构化时序执行流回放与单步断点恢复执行接口；前端开发 TaskReplayPlayer 回放播放器并嵌入任务详情页；前端开发 /settings/quota 配额管理台与设置中心 4 卡片导航</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>新增 TaskReplayPlayer 回放交互播放器组件（支持播放/暂停、倍速调节、时间轴 scrub 与 Payload 检查）；任务详情页嵌入回放流；新增 /settings/quota 工作区配额与限流控制台；设置中心首页导航升级为 4 卡片网格</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>新增 QuotaConfig 数据库模型与 quota_service 预算及限流治理；新增 endpoints/quota.py 与 endpoints/task_replay.py（/replay 与 /resume-from-step 接口）；支持断点恢复调度与审计日志联动</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>是(quota_configs)</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>pytest 全量 104 passed；前端测试 28 passed；前端 lint/build 0 errors 0 warnings 通过；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-任务执行回放与单步调试.md, docs/prd/PRD-工作区配额与限流治理.md；工单 C-108, C-109；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N107"/>
+  <autoFilter ref="A2:N109"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8260,6 +8404,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8293,8 +8293,152 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:13</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>C-108</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>31ed948</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、文档</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>docs: 更新变更追踪表、PRD 索引及回放断点恢复细节 (Batch 4)</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/api；backend/tests/test_task_replay.py</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:17</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>C-109</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>037e968</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>实现插件注册中心（D1）：引入 plugins 与 workspace_plugins 两张数据表；支持通过 JSON Manifest 注册外部工具、校验 Tool Schemas、按工作区挂载与动态开启/停用；前端开发 /settings/plugins 插件市场管理控制台、Manifest 预览抽屉与注册对话框；设置中心导航升级为 5 卡片网格</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>新增 /settings/plugins 插件管理控制台页面（支持搜索、Manifest 检查抽屉、启用/停用 Switch 与注册新插件 Modal）；设置中心首页导航升级为 5 卡片网格</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>新增 Plugin 与 WorkspacePlugin 数据库模型；新增 endpoints/plugins.py 端点（/plugins, /toggle, /active-tools）；RBAC 权限拦截与 audit_service 自动记录 plugin.toggle 审计日志</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>是(plugins, workspace_plugins)</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>pytest 全量 105 passed；前端测试 28 passed；前端 lint/build 0 errors 0 warnings 通过；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-插件注册中心.md；工单 C-110；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N109"/>
+  <autoFilter ref="A2:N111"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8406,6 +8550,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8437,8 +8437,152 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:17</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>C-110</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>9dbc783</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>docs: 更新变更追踪表、PRD 索引与 Excel 记录 (Batch 5)</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:22</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>C-111</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>19d4bdc</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、文档、其他、前端</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>实现工作流模板引擎（D2）：引入 workflow_templates 数据表与系统预设编排模板；支持多 Agent 协作流水线步骤节点（Node）定义与动态参数占位符（{{var}}）渲染；实现一键实例化生成 Task 任务并自动推入队列；前端开发 /workflows 工作流模板中心，支持模板卡片流、参数表单运行弹窗、节点查看抽屉与侧边栏导航集成</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>新增 /workflows 工作流模板中心（支持系统预设/自定义分类、节点链路查看抽屉、动态入参表单一键运行 Task 并在成功后自动跳转任务详情页、创建自定义工作流 Modal）；AppSidebar 侧边栏新增「工作流」主导航入口</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>新增 WorkflowTemplate 数据库模型；新增 endpoints/workflows.py 端点（/workflows, /workflows/{id}/run, /workflows/{id} DELETE）；支持变量替换、Task 实例化调度、系统预设保护与 audit_service 自动审计埋点</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>是(workflow_templates)</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>pytest 全量 106 passed；前端测试 28 passed；前端 lint/build 0 errors 0 warnings 通过；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-工作流模板引擎.md；工单 C-111；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N111"/>
+  <autoFilter ref="A2:N113"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8552,6 +8696,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8581,8 +8581,152 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:22</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>C-112</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>370021e</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>docs: 更新变更追踪表、PRD 索引与 Excel 记录 (Batch 6)</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:23</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>C-113</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>b4b25ff</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>docs: 更新 Phase 4 全量圆满达成项目接力文档 (HANDOFF)</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N113"/>
+  <autoFilter ref="A2:N115"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8698,6 +8842,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8725,8 +8725,80 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:26</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>C-114</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>b19cc89</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>docs: 统一更新全部 19 份 PRD 文档头部状态为已完成并刷新 HTML 与 Excel 追踪表</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N115"/>
+  <autoFilter ref="A2:N116"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8844,6 +8916,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8797,8 +8797,152 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:30</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>C-115</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>ec1f346</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>docs: 全面同步更新 README、PRODUCT、项目计划里程碑与变更报表</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:41</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>C-116</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>d61ac17</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>修复后端容器启动失败缺陷：优化 app/core/__init__.py 的导出内容，解除与 app/db/session.py 的部分循环初始化依赖，确保 Docker 镜像启动与 Uvicorn 服务平滑拉起</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>无变动</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>优化 backend/app/core/__init__.py 顶级导出，移除导致循环依赖的急切导入</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
+          <t>pytest 全量 106 passed；python -c 'from app.main import app' 成功导入；Docker backend 正常启动</t>
+        </is>
+      </c>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>修复 Docker Compose backend 容器退出报错</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N116"/>
+  <autoFilter ref="A2:N118"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -8917,6 +9061,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8941,8 +8941,80 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 23:42</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>C-117</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>ed960d5</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>docs: 更新变更追踪表与 Excel (C-113 BUG Fix)</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N118"/>
+  <autoFilter ref="A2:N119"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9063,6 +9135,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9013,8 +9013,80 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:14</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>C-118</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>f03830f</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、数据库、文档、前端</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>feat: 实现外部 Agent 软件接入与调度（integration_nodes 表、Bridge 适配器框架、Cursor Bridge、Codex CLI Bridge、动态 Software Dock）</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>frontend/src/components；frontend/src/hooks；frontend/src/types</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/api；backend/app/core；backend/app/db；backend/app/models；backend/app/schemas；backend/app/services；backend/app/websocket；backend/tests/test_database.py</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>是(integration_node)</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N119"/>
+  <autoFilter ref="A2:N120"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9136,6 +9208,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9085,8 +9085,152 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:16</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>C-119</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>0c9673a</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本同步变更追踪表与 PRD.html（118 行）</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:21</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>C-120</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>39d8f21</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 新增外部 Agent 软件接入章节、架构图更新、Roadmap E1</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N120"/>
+  <autoFilter ref="A2:N122"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9209,6 +9353,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9229,8 +9229,152 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:22</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>C-121</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>591e05d</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本同步变更追踪表与 PRD.html（120 行）</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:29</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>C-122</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>a0c5489</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 彻底重写，去除 AI 腔，回归工程文档风格</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N122"/>
+  <autoFilter ref="A2:N124"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9355,6 +9499,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:N130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9373,8 +9373,440 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:31</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>C-123</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>89c8a72</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本同步变更追踪表与 PRD.html（122 行）</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:34</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>C-124</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>49c9ecc</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 新增项目架构图（完整的后端分层与数据流）</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:06</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>C-125</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>7bebfcd</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>docs: 架构图从 ASCII 改为 Mermaid 渲染格式</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:09</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>C-126</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>b6a9e04</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>docs: 架构图重画，精简节点数量，GitHub 渲染更清晰</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 16:53</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>C-127</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>c8b31ac</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>docs: 新增外部 Agent 软件接入技术方案（接入分级、协议、实现顺序）</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 20:45</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>C-128</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>1931049</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 架构图优化为横向布局，分层更清晰</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N124"/>
+  <autoFilter ref="A2:N130"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9501,6 +9933,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N130"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9805,8 +9805,80 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:25</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>C-129</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>6f1a8f9</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、文档</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>feat: 补全外部 Agent 调度链路（任务回写 TaskStep、节点负载统计、审计日志、Bridge 目录契约统一）</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/api；backend/app/services；backend/tests/test_integrations.py</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N130"/>
+  <autoFilter ref="A2:N131"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -9939,6 +10011,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N131"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9877,8 +9877,152 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:30</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>C-130</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>579d578</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑变更追踪表与 PRD HTML，登记 C-129 外部 Agent 调度链路补全</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:44</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>C-131</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>09a6f8c</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 同步外部 Agent 调度链路，更新架构图（Bridge 层拆分、调度链路、目录约定、测试数 109）</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N131"/>
+  <autoFilter ref="A2:N133"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10012,6 +10156,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N133"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10021,8 +10021,152 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:48</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>C-132</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>55a6cf1</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本同步变更追踪表（131 行）与 PRD.html</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 23:11</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>C-133</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>c9e4dea</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>docs: 新增深色主题架构图 PNG/SVG + Mermaid 深色主题版，README 架构图双层呈现</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N133"/>
+  <autoFilter ref="A2:N135"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10158,6 +10302,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10165,8 +10165,152 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 23:19</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>C-134</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>61915f8</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 变更表行数同步 131 行，PRD.html 同步 133 条记录</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M136" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 23:27</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>C-135</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>015067b</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>docs: README 调度链路改为 Mermaid 流程图，更直观展示节点选择→执行→回写全链路</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N135"/>
+  <autoFilter ref="A2:N137"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10304,6 +10448,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10309,8 +10309,152 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 23:30</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>C-136</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>d250661</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步变更追踪表 135 行与 PRD.html 137 条记录</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 20:47</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>C-137</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>251e387</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、部署、文档、前端</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>群聊 @外部节点派发与 Cursor 桥接真实执行：@Cursor 等外部集成节点在群聊被 @ 提及时，MessageHub 优先匹配内部 Agent，未命中则按工作区查 integration_nodes 精确匹配节点名，命中即把任务派发给该节点（走 dispatch_task_to_node，不再走内部 LLM 编排）；CursorBridge.execute 从桩改为真实轮询任务工作目录 output.md，非空即回填结果、超时标记失败并落 events.jsonl；docker-compose 新增 ./data/bridges:/app/data/bridges bind mount（与 named volume 共存），让宿主 Cursor 客户端能看到任务目录；宿主新增 bridge/cursor_client.py 心跳保活 + 轮询打开 IDE + 读 output.md；前端 @ 菜单合并展示外部节点</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>chat-composer.tsx 新增 integrationNodes prop；mention-menu.tsx 新增 MentionEntry 类型与「外部节点」标识，按 name 插入 @Cursor；chat-page.tsx 接入 use-integrations 传入节点</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>message_hub.py 新增 _match_integration_node / _create_node_task / _run_node_dispatch，assigned_agent 改可选；cursor_bridge.py 真实轮询 output.md；config.py 已有 bridge_output_poll_timeout_seconds；schemas/message.py assigned_agent 改可选；新增 backend/tests/test_external_mention.py</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>否（复用 integration_nodes 表）</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr">
+        <is>
+          <t>pytest backend/tests 全量 103 passed；新增 3 用例全过；端到端：@Cursor→assigned_agent=None、step integration_dispatch:cursor:Cursor、写 output.md 后 task completed 且 result 含产出</t>
+        </is>
+      </c>
+      <c r="N139" s="5" t="inlineStr">
+        <is>
+          <t>Windows bind-mount 把宿主目录映射为容器内 root:755，故 backend 以 user: 0:0 运行以获写权限（本地开发）；PRD: docs/prd/PRD-外部节点群聊派发与Cursor桥接.md；子 Agent 独立验收待完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N137"/>
+  <autoFilter ref="A2:N139"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10450,6 +10594,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10419,22 +10419,22 @@
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>群聊 @外部节点派发与 Cursor 桥接真实执行：@Cursor 等外部集成节点在群聊被 @ 提及时，MessageHub 优先匹配内部 Agent，未命中则按工作区查 integration_nodes 精确匹配节点名，命中即把任务派发给该节点（走 dispatch_task_to_node，不再走内部 LLM 编排）；CursorBridge.execute 从桩改为真实轮询任务工作目录 output.md，非空即回填结果、超时标记失败并落 events.jsonl；docker-compose 新增 ./data/bridges:/app/data/bridges bind mount（与 named volume 共存），让宿主 Cursor 客户端能看到任务目录；宿主新增 bridge/cursor_client.py 心跳保活 + 轮询打开 IDE + 读 output.md；前端 @ 菜单合并展示外部节点</t>
+          <t>群聊 @外部节点派发与 Cursor 桥接真实执行：在群聊 @Cursor 等外部集成节点时，消息中枢优先匹配内部智能体，未命中则按工作区查询集成节点表，按节点名精确匹配，命中即把任务派发给该节点（走节点派发接口，不再走内部大模型编排）；光标桥接器的执行方法从占位桩改为真实轮询任务工作目录的产出文件，文件非空即回填结果，超时则标记失败并写入事件日志；编排文件新增宿主机与容器间的产出目录挂载，让宿主光标客户端能看到任务目录；宿主新增光标客户端脚本，负责心跳保活、轮询打开集成开发环境、读取产出文件；前端 @ 提及菜单合并展示外部节点</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>chat-composer.tsx 新增 integrationNodes prop；mention-menu.tsx 新增 MentionEntry 类型与「外部节点」标识，按 name 插入 @Cursor；chat-page.tsx 接入 use-integrations 传入节点</t>
+          <t>聊天输入组件新增外部节点入参；提及菜单组件新增「外部节点」标识类型，按节点名插入 @Cursor；聊天页接入节点列表并传入组件</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
         <is>
-          <t>message_hub.py 新增 _match_integration_node / _create_node_task / _run_node_dispatch，assigned_agent 改可选；cursor_bridge.py 真实轮询 output.md；config.py 已有 bridge_output_poll_timeout_seconds；schemas/message.py assigned_agent 改可选；新增 backend/tests/test_external_mention.py</t>
+          <t>消息中枢新增外部节点匹配、节点任务创建与派发协程；光标桥接器真实轮询产出文件；配置项已有桥接产出轮询超时；消息结构体的派发智能体字段改为可选；新增外部提及测试</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>否（复用 integration_nodes 表）</t>
+          <t>否（复用集成节点表）</t>
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr">
@@ -10444,17 +10444,89 @@
       </c>
       <c r="M139" s="5" t="inlineStr">
         <is>
-          <t>pytest backend/tests 全量 103 passed；新增 3 用例全过；端到端：@Cursor→assigned_agent=None、step integration_dispatch:cursor:Cursor、写 output.md 后 task completed 且 result 含产出</t>
+          <t>后端测试套件全量 103 项通过；新增 3 个用例全部通过；端到端验证：群聊 @Cursor 后任务派发步骤为「外部节点派发:cursor:Cursor」且运行中，写入产出文件后任务完成且结果包含产出内容</t>
         </is>
       </c>
       <c r="N139" s="5" t="inlineStr">
         <is>
-          <t>Windows bind-mount 把宿主目录映射为容器内 root:755，故 backend 以 user: 0:0 运行以获写权限（本地开发）；PRD: docs/prd/PRD-外部节点群聊派发与Cursor桥接.md；子 Agent 独立验收待完成</t>
+          <t>Windows 挂载把宿主目录映射为容器内 root:755，故后端以 root 身份（用户 0:0）运行以获写权限（本地开发）；需求文档见 docs/prd/PRD-外部节点群聊派发与Cursor桥接.md；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 20:52</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>C-138</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>7d601f2</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本同步外部节点派发特性的改动表与 PRD.html</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M140" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N139"/>
+  <autoFilter ref="A2:N140"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10596,6 +10668,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10525,8 +10525,152 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20 21:23</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>C-139</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>952c350</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>docs: 中文化 C-137 改动内容并同步生成脚本</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 21:40</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>C-140</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>18fb247</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>后端、部署、文档、其他</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>引入 Alembic 迁移治理并将数据库从 SQLite 迁移至 PostgreSQL：建立 Alembic 异步环境（env.py 按 DATABASE_URL 自动路由 sqlite/postgresql）并生成 19 张表的基线迁移；session.py 改为按 database_url 后缀选择 asyncpg/aiosqlite 驱动；config 默认 database_url 指向 PostgreSQL；Dockerfile 与 docker-compose 增加 postgres 服务与 asyncpg 依赖；新增 SQLite→PostgreSQL 数据迁移脚本（--dry-run + 行数校验）；补充共享测试 conftest fixture 与迁移正确性测试</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>alembic/ 环境与基线迁移脚本；app/db/session.py 按 URL 后缀选择驱动；app/core/config.py 默认 PostgreSQL；backend/Dockerfile 增加 asyncpg；docker-compose.yml 增加 db(postgres) 服务；scripts/migrate_sqlite_to_pg.py；tests/conftest.py 共享 fixture；tests/test_alembic_migrations.py</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>是（迁移至 PostgreSQL；不变更表结构，仅换存储引擎）</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>是（默认数据库由 SQLite 改为 PostgreSQL，需配置 DATABASE_URL 与 postgres 服务）</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
+          <t>后端全量 115 passed；前端 build/test/lint 0 error；基线迁移 upgrade head 建出 19 张表 + alembic_version；autogenerate 无遗漏；downgrade 回退正常</t>
+        </is>
+      </c>
+      <c r="N142" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-PostgreSQL迁移与Alembic迁移治理.md；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N140"/>
+  <autoFilter ref="A2:N142"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10669,6 +10813,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10669,8 +10669,152 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 21:41</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>C-141</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>e27f363</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本，将 PostgreSQL 迁移特性纳入变更追踪表与 PRD 阅读器</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M143" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:00</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>C-142</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>8dca104</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>ci: pytest 步骤使用 SQLite 测试数据库</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N142"/>
+  <autoFilter ref="A2:N144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10815,6 +10959,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N144"/>
+  <dimension ref="A1:N146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10813,8 +10813,152 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:00</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>C-143</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>c054905</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 CI SQLite 修复到变更追踪表与 PRD 阅读器</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:24</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>C-144</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>dec81dd</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>fix: 消除枚举 CHECK 约束导致的 Alembic autogenerate 噪音</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>backend/alembic/versions；backend/app/models</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N144"/>
+  <autoFilter ref="A2:N146"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -10961,6 +11105,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N146"/>
+  <dimension ref="A1:N147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>fix: 消除枚举 CHECK 约束导致的 Alembic autogenerate 噪音</t>
+          <t>修复枚举列 CHECK 约束在 SQLite 上导致 Alembic autogenerate 报 3 个 remove_constraint 噪音 diff，使 test_autogenerate_has_no_pending_changes 在 CI 失败；enums.py 改用 create_constraint=False（ORM 层 validate_strings 仍校验枚举值），并重建基线迁移 5291a2a7e49d 替换 e8c50310674b 以保持模型与迁移一致</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
@@ -10933,32 +10933,104 @@
       </c>
       <c r="J146" s="5" t="inlineStr">
         <is>
-          <t>backend/alembic/versions；backend/app/models</t>
+          <t>backend/app/models/enums.py；backend/alembic/versions/5291a2a7e49d_baseline_initial_schema_19_tables.py</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否（仅调整枚举列 CHECK 约束生成策略，未改表结构或列类型）</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否（迁移脚本本身未 emit CHECK，升级不产生破坏性 DDL；生产 PG 枚举列为 VARCHAR，原设计未依赖 DB 级 CHECK）</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>test_alembic_migrations.py 3 passed（含 test_autogenerate_has_no_pending_changes）；后端全量 115 passed</t>
         </is>
       </c>
       <c r="N146" s="5" t="inlineStr">
         <is>
+          <t>SQLite + Alembic autogenerate 对列内 CHECK 约束的已知反射噪音；选放弃 DB 级 CHECK 换取 CI 可移植性，应用层校验仍有效</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:26</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>C-145</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>0f62364</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>docs: 将枚举 CHECK 修复(dec81dd)纳入变更追踪表并修正标注</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M147" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N146"/>
+  <autoFilter ref="A2:N147"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11107,6 +11179,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N147"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11029,8 +11029,80 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:34</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>C-146</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>1543d49</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>WorkBuddy</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>docs: 修正 dec81dd 变更表登记位置，C-144 标注 db/breaking 为否</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N147"/>
+  <autoFilter ref="A2:N148"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11180,6 +11252,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId146"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11101,8 +11101,152 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:41</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>C-147</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>f21b578</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本将 1543d49 纳入变更追踪表(C-146)</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:53</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>C-148</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>b57b232</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步 README 与今日 PostgreSQL/Alembic 迁移治理改动</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N148"/>
+  <autoFilter ref="A2:N150"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11253,6 +11397,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId148"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N150"/>
+  <dimension ref="A1:N152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11245,8 +11245,152 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:55</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>C-149</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>b56d4e5</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本将 README 同步提交纳入变更表(C-148)</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 23:19</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>C-150</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>bf48f2a</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>optimize: Codex bridge 配置化与进程树清理加固</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/core；backend/app/services；backend/tests/test_codex_bridge.py</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N150"/>
+  <autoFilter ref="A2:N152"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11399,6 +11543,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N152"/>
+  <dimension ref="A1:N154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11389,8 +11389,152 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 23:20</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>C-151</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>74bc06b</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步变更表至 C-150</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M153" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 23:32</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>C-152</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>ef2afbb</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>optimize: 新增混合模式启动脚本 start-local.bat（P0 拓扑定案）</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N152"/>
+  <autoFilter ref="A2:N154"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11545,6 +11689,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId152"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N154"/>
+  <dimension ref="A1:N156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11533,8 +11533,152 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21 23:33</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>C-153</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>8d2f9ff</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步变更表至 C-152</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22 11:47</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>C-154</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>11b660a</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库、其他、前端</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>外部任务包元数据与状态机补齐（P2）：dispatch 支持验收条件/路径约束/测试命令/预算，新增 waiting_approval 状态、dispatch 异步化、取消接口与孤儿恢复</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>TaskStatus 加 waiting_approval；task-status-badge/message-bubble 补「等待审批」映射；task-utils 非终态 rank</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>bridge.py 任务包扩展；integration_service.py DispatchPackage/结果校验/取消/孤儿恢复；enums.py 加 WAITING_APPROVAL；integrations.py dispatch 异步化(422 预校验)；message_hub.py schedule_node_dispatch；tasks.py 新增 POST /{id}/cancel；Alembic 迁移 f788539de554（status 列 VARCHAR 9→16）</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>是（tasks.status 枚举加值 waiting_approval，列类型加宽需迁移）</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>否（dispatch 响应保留旧字段仅新增 status=accepted）</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
+          <t>后端 128 passed（新增 9）；前端 build+test 28 passed+lint 干净</t>
+        </is>
+      </c>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-外部任务包元数据与状态机补齐.md；budget_turns 本轮透传记录，执行器级控制留 P4/P5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N154"/>
+  <autoFilter ref="A2:N156"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11691,6 +11835,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11677,8 +11677,656 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22 11:51</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>C-155</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>a63089c</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>docs: 同步变更表至 C-154 并补充 P2 PRD 索引</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:50</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>C-156</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>5d5a7cb</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>删除 orchestrator 中重复定义的 _build_task_context_messages 死代码</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>app/core/orchestrator.py 删除约 60 行重复定义的死代码</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="5" t="inlineStr">
+        <is>
+          <t>纯删除死代码，无行为变化（-60 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:50</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>C-157</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>7768e56</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>修复成本统计日趋势在 PostgreSQL 下报错：按数据库方言选择日期分组函数（PostgreSQL 用 to_char，SQLite 保持 strftime）</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>endpoints/cost_stats.py 日趋势日期分组表达式按 db.bind 方言选择 to_char/strftime</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr">
+        <is>
+          <t>仅后端 1 文件（+8/-1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:50</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>C-158</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>c1d6dbb</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>WebSocket 支持 JWT 凭证认证并新增 ws_allowed_origins Origin 白名单配置：握手凭证接受静态 API Token 或有效 JWT，未配置静态 Token 时保持开放模式兼容；白名单非空时校验握手 Origin</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>websocket/router.py Origin 白名单校验 + 凭证校验切换；core/security.py 新增 websocket_credential_is_valid（静态 Token 或 JWT）；core/config.py 新增 ws_allowed_origins 配置</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>否（白名单默认为空不拦截；无静态 Token 时保持开放）</t>
+        </is>
+      </c>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
+          <t>新增 tests/test_websocket_auth.py（+205）</t>
+        </is>
+      </c>
+      <c r="N160" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:52</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>C-159</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>dfc3dcc</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>REST 老路由 tasks/agents/provider_keys/custom_models 补齐 RBAC 用户级鉴权：新增条件守卫，仅当请求携带有效用户 JWT 时按工作区角色矩阵校验，静态 Token 与开放模式保持原有兼容行为</t>
+        </is>
+      </c>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>新增 api/rbac_compat.py 兼容守卫（有 JWT 才校验，403 权限不足提示）；tasks/agents/provider_keys/custom_models 四组端点接入</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>否（静态 token/开放模式保持兼容）</t>
+        </is>
+      </c>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>新增 tests/test_rest_rbac.py（+379）</t>
+        </is>
+      </c>
+      <c r="N161" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:10</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>C-160</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>e140d7c</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>前端统一工作区选择逻辑并修复任务刷新定时器泄漏</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>新增 lib/active-workspace.ts 共享工作区选择工具；use-agent-console/use-chat/use-workspaces 统一工作区解析；use-tasks 修复刷新定时器泄漏</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M162" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="5" t="inlineStr">
+        <is>
+          <t>纯前端改动（6 文件 +139/-24）</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:22</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>C-161</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>36a0c21</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>配额硬熔断与速率限制接入任务创建链路：群聊派发（message_hub）与工作流运行（workflows.run）两处拦截，超额或超每分钟速率返回 429；未开启硬熔断时保持软性语义仅记录日志</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>quota_service 新增 check_workspace_quota 与进程内每分钟滑动窗口限流；message_hub 派发前 _enforce_quota；endpoints/workflows.py run 前拦截</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>是（任务创建链路超限新增 429 拒绝）</t>
+        </is>
+      </c>
+      <c r="M163" s="5" t="inlineStr">
+        <is>
+          <t>新增 tests/test_quota_enforcement.py（+257）</t>
+        </is>
+      </c>
+      <c r="N163" s="5" t="inlineStr">
+        <is>
+          <t>速率限制为进程内滑动窗口，多实例分布式版留 TODO（Redis 固定窗口/令牌桶）</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:22</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>C-162</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>8454f84</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>插件工具注入 Agent 函数调用循环并落地可扩展执行钩子：插件声明式工具运行时合并进 Function Calling 规格，经注册执行器分发；未注册 executor 时诚实返回 not implemented 而非伪造结果</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>services/tools.py 新增 register_plugin_tool_executor 钩子与插件工具规格合并/参数校验/分发；orchestrator.py 工具循环接入插件工具</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M164" s="5" t="inlineStr">
+        <is>
+          <t>新增 tests/test_plugin_tools.py（+512）</t>
+        </is>
+      </c>
+      <c r="N164" s="5" t="inlineStr">
+        <is>
+          <t>执行边界：工具服务不直接发起外部 webhook 调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:30</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>C-163</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>089be34</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>refresh token 服务端记录与吊销：登录/注册签发时落库，刷新时校验吊销状态，logout 真实吊销 refresh token（此前仅前端清除）</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>新增 RefreshToken 模型与 Alembic 迁移 a1b2c3d4e5f6（refresh_tokens 表）；auth 端点签发落库/刷新校验吊销/登出标记 revoked；schemas 新增 LogoutRequest</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>是(refresh_tokens)</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>否（无服务端记录的旧 token 仍可刷新，向后兼容）</t>
+        </is>
+      </c>
+      <c r="M165" s="5" t="inlineStr">
+        <is>
+          <t>新增 tests/test_refresh_revocation.py（+154）</t>
+        </is>
+      </c>
+      <c r="N165" s="5" t="inlineStr">
+        <is>
+          <t>签发时顺带清理该用户过期记录</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N156"/>
+  <autoFilter ref="A2:N165"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -11837,6 +12485,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N165"/>
+  <dimension ref="A1:N168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12325,8 +12325,224 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 21:43</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>C-164</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>73609d6</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>docs: 回写滞后文档并补登 8 项提交变更表记录</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M166" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 21:54</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>C-165</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>e1203d9</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>后端、其他、前端</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>任务轨迹 WebSocket 实时推送与开发者/用户双层视图：新增 task.trace_updated 事件，orchestrator 在步骤/模型调用保存后广播轻量增量轨迹事件，前端直接合并免刷新；任务详情页新增视图切换，用户视图隐藏 Token/成本/上下文快照/步骤输入输出与轨迹明细</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>task-detail-page.tsx 视图切换与敏感内容条件渲染；use-tasks.ts useTaskDetail 合并轨迹；task-utils.ts 新增 mergeTraceEvent；types/task.ts 增事件类型</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
+        <is>
+          <t>websocket/events.py 加 task.trace_updated；execution_trace.py 提取 step_trace_event/call_trace_event 单事件构建；orchestrator.py _emit_trace_update 广播</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M167" s="5" t="inlineStr">
+        <is>
+          <t>后端 168 passed；前端 31 passed + lint 0 error + build 通过</t>
+        </is>
+      </c>
+      <c r="N167" s="5" t="inlineStr">
+        <is>
+          <t>PRD-单任务上下文连续性 §16 FR8/FR9 更新为已落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:00</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>C-166</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>7eacddf</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>后端、文档、其他</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>Provider Key 信封加密：provider_credentials.api_key 由明文改为 Fernet 信封加密存储（v1: 前缀），主密钥由 JWT 密钥经 PBKDF2 派生；存量明文透传兼容、零表结构迁移；模型调用读取链路自动解密</t>
+        </is>
+      </c>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>新增 core/crypto.py（encrypt/decrypt/is_encrypted + PBKDF2 主密钥派生）；provider_keys.py 写入加密、掩码前解密；litellm_service.get_db_api_keys 解密（单条失败跳过）；requirements 补 cryptography</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>否（复用 provider_credentials Text 列，v1: 前缀，零迁移）</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>否（存量明文兼容）</t>
+        </is>
+      </c>
+      <c r="M168" s="5" t="inlineStr">
+        <is>
+          <t>后端 175 passed（新增 7）；端点掩码/存在性测试通过</t>
+        </is>
+      </c>
+      <c r="N168" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-ProviderKey信封加密.md；生产须显式配置 jwt_secret_key，轮换主密钥需重录 Key；Docker 需重建纳入 cryptography</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N165"/>
+  <autoFilter ref="A2:N168"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -12494,6 +12710,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="H166" s="5" t="inlineStr">
         <is>
-          <t>docs: 回写滞后文档并补登 8 项提交变更表记录</t>
+          <t>回写滞后文档并补登历史提交变更表：HANDOFF 更新为 20 表/168 测试/PostgreSQL 现状并补 refresh_tokens、integration_nodes 两表；两份已上线 PRD 状态由待实施改为已完成；项目计划数据层描述改 PostgreSQL；CURATED 补登 C-155~C-163 共 8 项提交</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>重跑 generate_change_log.py + build_prd_html.py：163 行/23 份 PRD 生成成功</t>
         </is>
       </c>
       <c r="N166" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>纯文档与生成脚本同步，无代码行为变化</t>
         </is>
       </c>
     </row>
@@ -12460,12 +12460,12 @@
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
-          <t>后端 168 passed；前端 31 passed + lint 0 error + build 通过</t>
+          <t>后端 168 passed；前端 31 passed + lint 0 error + build 通过；浏览器 A/B：开发者视图全量展示，用户视图隐藏 Token/成本/回放/快照/载荷</t>
         </is>
       </c>
       <c r="N167" s="5" t="inlineStr">
         <is>
-          <t>PRD-单任务上下文连续性 §16 FR8/FR9 更新为已落地</t>
+          <t>PRD-单任务上下文连续性 §16 FR8/FR9 更新为已落地；子 Agent 独立验收通过；A/B 发现回放器漏门控由 3b07f14 修复</t>
         </is>
       </c>
     </row>
@@ -12537,12 +12537,156 @@
       </c>
       <c r="N168" s="5" t="inlineStr">
         <is>
-          <t>PRD: docs/prd/PRD-ProviderKey信封加密.md；生产须显式配置 jwt_secret_key，轮换主密钥需重录 Key；Docker 需重建纳入 cryptography</t>
+          <t>PRD: docs/prd/PRD-ProviderKey信封加密.md；生产须显式配置 jwt_secret_key，轮换主密钥需重录 Key；Docker 需重建纳入 cryptography；子 Agent 独立验收通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:01</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>C-167</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>854078d</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>登记 C-164/C-165 并重跑生成脚本：CURATED 补登任务轨迹双层视图与 Provider Key 信封加密两条 Requirement，重生改动表、xlsx 与 PRD.html（24 份）</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M169" s="5" t="inlineStr">
+        <is>
+          <t>166 行/24 份 PRD 生成成功</t>
+        </is>
+      </c>
+      <c r="N169" s="5" t="inlineStr">
+        <is>
+          <t>纯文档与生成脚本同步</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>C-168</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>3b07f14</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>修复用户视图遗漏隐藏任务时序回放器：浏览器 A/B 验证发现用户视图仍显示回放器（含累计成本与输入/输出 Payload），将其纳入开发者视图门控</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>task-detail-page.tsx 回放器改为仅开发者视图渲染</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M170" s="5" t="inlineStr">
+        <is>
+          <t>浏览器 A/B 复验：用户视图回放器/成本/载荷全部隐藏；前端 31 passed + lint 0 + build 通过</t>
+        </is>
+      </c>
+      <c r="N170" s="5" t="inlineStr">
+        <is>
+          <t>C-164 FR9 收尾；A/B 验证发现的展示层遗漏</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N168"/>
+  <autoFilter ref="A2:N170"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -12713,6 +12857,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N170"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12685,8 +12685,296 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:22</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>C-169</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>905f858</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>docs: 补齐守则闭环——验收结论写回改动表并登记 A/B 补救提交</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M171" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:32</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>C-170</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>0529d2c</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、部署</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>启用独立 Worker 与事件总线调度链路：app/worker.py 此前已实现完整的队列消费逻辑，但全仓库无任何启动入口，Phase 2/3 的能力从未真正运行。本次新增 docker-compose worker 服务承载任务消费；task_execution_mode 默认值由 inline 改为 queue，任务经持久化队列由独立进程执行；compose 与本地脚本注入 EVENT_BUS_ENABLED / DISTRIBUTED_LOCK_ENABLED 打开 Redis 事件总线与分布式锁；Worker 进程内注册事件发布器，修复 queue 模式下任务事件静默丢弃导致前端实时推送整体失效的阻断问题</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>无改动</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>app/core/config.py 默认 queue + 新增续租/回收间隔配置；app/worker.py run_worker 内 build_event_relay(...).start()/stop() 注册事件出口（FR8）；docker-compose.yml 新增 worker 服务并以 YAML anchor 复用 backend 环境变量；start-local.bat 新增 [6/7] Worker 窗口；.env.example 补齐开关与中文注释</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>否（不变更表结构）</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>是（默认执行模式由 API 进程内 inline 改为队列 queue；未启 Worker 时任务会停在 pending。可通过 TASK_EXECUTION_MODE=inline 一键回退）</t>
+        </is>
+      </c>
+      <c r="M172" s="5" t="inlineStr">
+        <is>
+          <t>后端全量 181 passed（含新增 6 例）；docker compose config --services 输出 5 服务含 worker；python -c 'import app.worker' 退出码 0；冒烟确认 get_settings() 生效 queue / event_bus_enabled=True / distributed_lock_enabled=True</t>
+        </is>
+      </c>
+      <c r="N172" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-独立Worker与事件总线链路启用.md；R1（Worker 事件出口）经复核为启用 queue 的阻断项，已由 FR8 一并修复；DISTRIBUTED_LOCK_ENABLED 为预留开关，当前无消费方，不得写成「分布式锁已启用」</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:32</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>C-171</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>b8e5fcf</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>修复任务租约缺续租与失联回收不及时缺陷：TaskService 此前只有 enqueue/claim_next/complete/fail/recover，没有 renew，任何跑得比租约更久的任务都会在半途被 recover 判定为失联、重新入队并被执行第二次；且 recover 仅在 Worker 启动时调用一次，运行期不再回收，Worker 崩溃留下的过期租约会一直挂着直到下次重启。本次新增 renew 条件更新租约、Worker 执行期续租协程（租约丢失后自行退出不再触碰该队列项）、以及主循环定时失联回收；worker.py 同时落地 C-170 FR8 的 Worker 侧事件出口注册（queue 模式下缺此注册会导致任务事件全部静默丢弃、前端实时推送整体失效），故两处改动合并在本次提交</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>无改动</t>
+        </is>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>app/services/task_service.py 新增 renew()；app/worker.py 新增 _renew_lease 续租协程与 _sweep_expired_leases，_consume_once 执行期挂续租任务并在 finally 中取消，run_worker 主循环按间隔回收；config 新增 worker_lease_renew_interval_seconds(30) / worker_recover_interval_seconds(60)；新增 tests/test_worker_lease.py</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>否（复用 task_queue_items 既有租约字段）</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M173" s="5" t="inlineStr">
+        <is>
+          <t>新增 6 个测试全部通过：test_task_queue 3 例（续租后免于回收 / 错误 token 与已完成项拒绝续租 / 未续租则被回收）与 test_worker_lease 3 例（执行期租约被延长 / 租约丢失后续租协程自行退出且只重试一次 / 定时 sweep 回收失联租约）；后端全量 181 passed，无新增失败</t>
+        </is>
+      </c>
+      <c r="N173" s="5" t="inlineStr">
+        <is>
+          <t>已知未解决：orchestrator.execution_token 与 task_queue_items.lease_token 两套租约互不同步，需架构决策统一，归入 C-17x；另新增 6 个测试（队列 3 + Worker 3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:33</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>C-172</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>4c5ba6b</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>修正项目计划里程碑标记与现状数据口径：Phase 2 标注为 C-170 起默认启用并补「可续租」；Phase 3 由「已达成」降级为「部分达成」并列出两项仍缺能力（前端未消费 workspace.snapshot、配额限流仍为单实例内存计数）；Phase 4 完成标志由 18 张表更正为实际 20 张表；新增落地状态核查说明并引用全仓库审查报告</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M174" s="5" t="inlineStr">
+        <is>
+          <t>纯文档口径修正，无代码行为变化；后端全量 181 passed 不受影响</t>
+        </is>
+      </c>
+      <c r="N174" s="5" t="inlineStr">
+        <is>
+          <t>纯文档口径修正，无代码行为变化；审查报告见 docs/代码与计划落地差距审查报告-20260828.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N170"/>
+  <autoFilter ref="A2:N174"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -12859,6 +13147,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="N172" s="5" t="inlineStr">
         <is>
-          <t>PRD: docs/prd/PRD-独立Worker与事件总线链路启用.md；R1（Worker 事件出口）经复核为启用 queue 的阻断项，已由 FR8 一并修复；DISTRIBUTED_LOCK_ENABLED 为预留开关，当前无消费方，不得写成「分布式锁已启用」</t>
+          <t>PRD: docs/prd/PRD-独立Worker与事件总线链路启用.md；R1（Worker 事件出口）经复核为启用 queue 的阻断项，已由 FR8 一并修复；DISTRIBUTED_LOCK_ENABLED 为预留开关，当前无消费方，不得写成「分布式锁已启用」；容器实跑验证（AC1/AC4/AC8）因 Docker Desktop 守护进程未启动未执行，仅完成配置层验证（docker compose config --services 输出 5 服务含 worker）；守则验收：子 Agent 因平台限流（HTTP 429）连续派发失败，改由主 Agent 按同一清单自检通过</t>
         </is>
       </c>
     </row>
@@ -12973,8 +12973,80 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:37</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>C-173</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>9d92867</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>其他、后端、部署、文档</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>docs: 修正变更编号偏移（C-169~C-171 顺延为 C-170~C-172）并重跑生成脚本</t>
+        </is>
+      </c>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="5" t="inlineStr">
+        <is>
+          <t>backend/app/core；backend/app/services；backend/app/worker.py</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M175" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N174"/>
+  <autoFilter ref="A2:N175"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -13151,6 +13223,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId173"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N175"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12820,7 +12820,7 @@
       </c>
       <c r="M172" s="5" t="inlineStr">
         <is>
-          <t>后端全量 181 passed（含新增 6 例）；docker compose config --services 输出 5 服务含 worker；python -c 'import app.worker' 退出码 0；冒烟确认 get_settings() 生效 queue / event_bus_enabled=True / distributed_lock_enabled=True</t>
+          <t>后端全量 181 passed（含新增 6 例）；A/B 对比（git worktree 检出改动前 905f858 跑同一探针脚本对照）：执行模式默认 inline→queue、compose 服务 4→5（新增 worker）、Worker 事件出口注册 False→True、定时失联回收 False→True、TaskService 方法 5→6（新增 renew）；冒烟：API 实启动 GET /api/v1/health 返回 status=ok、Worker 进程 python -m app.worker 存活 15 秒零异常、事件中继 enabled=false/true 两种模式 start()/stop() 均 OK；配置层 docker compose config --services 输出 5 服务含 worker</t>
         </is>
       </c>
       <c r="N172" s="5" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>新增 6 个测试全部通过：test_task_queue 3 例（续租后免于回收 / 错误 token 与已完成项拒绝续租 / 未续租则被回收）与 test_worker_lease 3 例（执行期租约被延长 / 租约丢失后续租协程自行退出且只重试一次 / 定时 sweep 回收失联租约）；后端全量 181 passed，无新增失败</t>
+          <t>新增 6 个测试全部通过（test_task_queue 3 例 + test_worker_lease 3 例）；A/B 租约场景对照（租约仅剩 1 秒、任务继续跑 2.5 秒后触发 sweep）：A 态（改动前）无 renew 可调用，sweep 回收 1 条、队列项回到 queued、租约字段清空 → 原 Worker 仍在跑而他人可领走同一任务；B 态（改动后）续租成功，sweep 回收 0 条、状态保持 leased、租约剩余 597.5 秒 → 不会被重复消费；后端全量 181 passed，无新增失败</t>
         </is>
       </c>
       <c r="N173" s="5" t="inlineStr">
@@ -13045,8 +13045,80 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:40</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>C-174</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>7a985a1</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>docs: 重跑生成脚本同步改动表与 PRD.html（173 行 / 25 份 PRD，登记编号修正）</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N175"/>
+  <autoFilter ref="A2:N176"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -13224,6 +13296,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N176"/>
+  <dimension ref="A1:N180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13117,8 +13117,296 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:11</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>C-175</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>505b0bb</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>docs: 补登 C-170/C-171 的 A/B 对比与冒烟测试结论并重跑生成脚本</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M177" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 11:38</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>C-176</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>5a22954</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F178" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>事件总线容错缺陷修复：发布侧 publish 失败不再冒泡击穿业务调用方（本地投递在前，仅警告吞没）；订阅侧 _relay_loop 断开后按 1s→30s 指数退避自动重连，消除「Redis 恢复后跨实例推送静默失效直到重启」缺陷</t>
+        </is>
+      </c>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>distributed.py publish 包 try/except 吞没；relay.py __init__ 增 retry_base_delay/retry_max_delay，_relay_loop 改指数退避重连循环</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M178" s="5" t="inlineStr">
+        <is>
+          <t>后端 185 passed（新增容错用例 2 个，既有 21 例总线/中继测试全绿）</t>
+        </is>
+      </c>
+      <c r="N178" s="5" t="inlineStr">
+        <is>
+          <t>修复差距审查报告 §14 R2（P1）；Redis 不可用降级语义见 PRD-独立Worker §14 R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 11:38</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>C-177</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>a95058a</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>后端、前端</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>WebSocket 连接即下发工作区快照，前端断线重连状态对账：后端握手成功后仅向新客户端下发 workspace.snapshot（任务/Agent/最近消息），前端按 id 修补既有列表，兑现 Phase 3「断线重连后重新同步最新任务与消息状态」验收；删除无调用方的 build_and_broadcast_snapshot 死代码</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>task-utils.ts 新增 applySnapshotTasks；types/task.ts 与 types/chat.ts 增 workspace.snapshot 变体；use-tasks/use-chat 消费快照</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>websocket/router.py 连接后下发快照；删除 snapshot.py build_and_broadcast_snapshot 死代码；__init__.py 同步</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M179" s="5" t="inlineStr">
+        <is>
+          <t>后端 185 passed（新增 test_ws_snapshot 2 例）；前端 34 passed + lint 0 + build 通过</t>
+        </is>
+      </c>
+      <c r="N179" s="5" t="inlineStr">
+        <is>
+          <t>补齐差距审查报告 §2.2（P1-3）；Phase 3 验收对账闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 11:49</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>C-178</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>14a8406</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>工作区快照任务载荷补 conversation_id：前端 use-chat 按 conversation_id 过滤快照任务，后端载荷缺该字段导致群聊侧任务对账静默失效，补齐字段并加测试断言</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t>websocket/snapshot.py 任务载荷补 conversation_id；test_ws_snapshot.py 增断言</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M180" s="5" t="inlineStr">
+        <is>
+          <t>后端 test_ws_snapshot 2 passed</t>
+        </is>
+      </c>
+      <c r="N180" s="5" t="inlineStr">
+        <is>
+          <t>A/B 集成审查发现的载荷字段遗漏</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N176"/>
+  <autoFilter ref="A2:N180"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -13297,6 +13585,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N180"/>
+  <dimension ref="A1:N183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13405,8 +13405,224 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 11:57</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>C-179</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>a869f8c</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>docs: 回写文档一致性欠账并登记快照/总线容错三项提交</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M181" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 12:54</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>C-180</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>2567b98</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>其他、部署</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>修复容器模式启动崩溃：宿主 .env 的 sqlite DATABASE_URL 插值泄漏进容器旁路 postgres，双容器并发 init_db 跑 alembic 触发 table already exists。DATABASE_URL 改用 COMPOSE_DATABASE_URL（对齐 COMPOSE_REDIS_URL 惯例），新增一次性 migrate 服务独占迁移，backend/worker 等待其完成，应用内 init_db 保留为幂等空转兼容 standalone</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>docker-compose.yml 新增 migrate 一次性服务（service_completed_successfully 门控 backend/worker）；.env.example 补 COMPOSE_DATABASE_URL</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M182" s="5" t="inlineStr">
+        <is>
+          <t>容器实跑：5 常驻服务全 healthy、migrate 三迁移按序完成、backend/worker 无竞争崩溃；AC1/AC2 通过</t>
+        </is>
+      </c>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29 容器级验证（C-170 AC）发现并修复；PRD-独立Worker §9.1 已回写</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 12:54</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>C-181</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>4ccb5a4</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>消除僵尸队列条目：claim_next 仅匹配 PENDING 任务，run_task 正常返回失败（编排器已置 FAILED）时旧逻辑重新入队产生既不可再领取亦非终态的僵尸项。TaskService.fail 新增 retry 开关，worker 终结分支 retry=False 直接落 dead，异常分支保留有界重试</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>services/task_service.py fail(retry=...)；worker.py _consume_once 终结分支 retry=False；tests/test_task_queue.py 补根因+修复 2 个回归测试</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>否（fail 默认 retry=True 行为不变）</t>
+        </is>
+      </c>
+      <c r="M183" s="5" t="inlineStr">
+        <is>
+          <t>后端 187 passed；容器实跑 AC4：入队→worker 跨进程 leased（attempt=1）→dead 终态，修复前僵尸 queued 与修复后 dead 前后对照</t>
+        </is>
+      </c>
+      <c r="N183" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-29 容器级验证发现；与统一两套租约体系（C-17x 架构债）相关但独立修复</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N180"/>
+  <autoFilter ref="A2:N183"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -13589,6 +13805,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId181"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N183"/>
+  <dimension ref="A1:N188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13621,8 +13621,368 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29 13:00</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>C-182</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>bb87032</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>文档、其他</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>docs: 容器级验证记录与 C-170 AC 结论回写，登记两个容器缺陷修复（C-180/C-181）</t>
+        </is>
+      </c>
+      <c r="I184" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M184" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="5" t="inlineStr">
+        <is>
+          <t>docs/AB与冒烟测试记录-20260829.md 新增容器级验证结论；PRD-独立Worker §9.1 回写</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:31</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>C-183</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>2b15a20</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>后端、文档、其他</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>插件 Webhook 工具执行器与任务终态出站通知：插件工具此前只有声明没有执行（占位执行器返回 not implemented）。本次 httpx 出站 + HMAC-SHA256 请求签名（X-Webhook-Signature 覆盖完整 body）+ asyncio.wait_for 超时 + 网络错误/5xx 有界重试，never-raise 契约；执行器经全局钩子在 API lifespan 与 Worker 启动时各注册一次；任务进入终态后向工作区插件配置的 webhook_url 推送摘要（无配置零请求，失败仅记日志不影响状态事务）</t>
+        </is>
+      </c>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>schemas/plugin.py PluginToolDefinition 加 headers/secret、PluginManifest 加 secret；新建 services/webhook.py（call_webhook/plugin_webhook_executor/notify_workspace_webhooks/register_webhook_executor）；services/tools.py 新增 register_global_plugin_tool_executor 全局执行器钩子，load_active_plugin_tools 带 headers/secret（工具级&gt;manifest 级）；orchestrator.update_task_status 终态后 _notify_task_terminal；main.py lifespan 与 worker.py 启动注册；requirements.txt 加 httpx&gt;=0.28；新增 tests/test_webhook.py 20 例</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>否（配置存于 manifest_json/config_json 既有 JSON 内）</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M185" s="5" t="inlineStr">
+        <is>
+          <t>后端全量 207 passed（含新增 test_webhook.py 20 例）；签名正确性/超时/非 2xx 不抛/重试后成功/终态通知扇出均有断言</t>
+        </is>
+      </c>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-插件Webhook执行器与出站通知.md；语义变化：无 endpoint 的插件工具错误文案 not implemented → no endpoint or base_url configured（test_plugin_tools 已同步）</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 21:31</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>C-184</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>e5f8f81</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>修复后端测试环境不封闭：app.core.config 的 env_file 含 ../.env，开发者根目录 .env 的 sqlite DATABASE_URL 泄漏进测试进程，TestClient lifespan 对开发库跑 alembic 触发 table already exists（基线 62 errors + 1 failed）。conftest.py pytest_configure 钉一次性临时 DATABASE_URL（与既有三个环境开关同模式，setdefault 保留显式覆盖），基线恢复全绿</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" s="5" t="inlineStr">
+        <is>
+          <t>backend/tests/conftest.py pytest_configure 增 DATABASE_URL setdefault（tempdir 下带 uuid 的一次性 sqlite 文件）</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M186" s="5" t="inlineStr">
+        <is>
+          <t>基线 62 errors + 1 failed → 187 passed 全绿</t>
+        </is>
+      </c>
+      <c r="N186" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1（C-183~C-186）前置准备；仅测试环境，不影响生产路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:10</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>C-185</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>cee376c</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>后端、前端</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>HITL 人工审批节点：多 agent 流程 review 完成后、final 之前支持人工审批——落 human_approval/waiting 步骤并把任务置 WAITING_APPROVAL，用独立 session 每 2s 轮询该步骤状态（跨进程 DB 解耦，等待期不持有未提交事务），3600s 超时按驳回；通过则回 RUNNING 继续 final，驳回则落 rejected 并置 FAILED。新增 approve/reject 端点（非 WAITING_APPROVAL 返回 409，admin 及以上可操作，写审计日志）；前端任务时间线在等待审批时渲染「通过/驳回」按钮</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>task-detail-page.tsx TaskSteps 等待审批渲染「通过/驳回」按钮（复用页面 refetch）；task-format.ts 补 human_approval 标签与 waiting/approved/rejected 文案</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>orchestrator._run_multi_agent_task 加 requires_approval 参数 + _task_requires_approval（按描述头反查工作流模板检测 human_approval 节点）+ _request_approval/_wait_approval（DB 轮询）；endpoints/tasks.py 新增 POST /{task_id}/approve、/{task_id}/reject；schemas/workflow.py WorkflowNode 加 type 字段（agent|human_approval）；WAITING_APPROVAL 枚举复用既有（enums.py）；新增 tests/test_human_approval.py 6 例</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>否（复用 task_steps）</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>是（TaskStatus 语义新增 waiting_approval 中间态；前端状态联合已同步）</t>
+        </is>
+      </c>
+      <c r="M187" s="5" t="inlineStr">
+        <is>
+          <t>后端全量 230 passed（含新增 6 例）；前端 lint 0 error、build 成功；覆盖挂起→通过→继续、驳回→FAILED、非审批状态 409、轮询跨 session 解耦</t>
+        </is>
+      </c>
+      <c r="N187" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-人工审批节点.md；前端按钮全员可见（页面无角色上下文），后端 403 兜底，后续收紧；与队列租约统一问题归 C-17x</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:11</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>C-186</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>b272f5d</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>后端、数据库</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>DAG 工作流引擎：run_workflow_template 此前把所有节点压成一段 prompt 交给单 agent。本次重写为真 DAG 编排——Kahn 分层拓扑排序（兼容 dependencies/depends_on，环/未知依赖/缺 id/重复 id 报中文错误）、层内 asyncio.gather 并行执行、每节点经 save_task_step 落库并写 node_id/dependencies_json/order_index；新建 WorkflowRun 运行记录（snapshot 快照、running→completed/failed）；失败中止后续层、已完成层保留。响应契约不变（仍返回 task_id）。集成 C-184：type=human_approval 节点走审批挂起而非模型调用</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>-（DAG 画布留 Phase 3）</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>models/workflow.py 新增 WorkflowRun 表；models/task.py TaskStep 加 node_id/dependencies_json/order_index 三列；Alembic 迁移 b7c9d1e3f5a7（SQLite batch_alter_table 双兼容，downgrade 完整回滚）；新建 services/dag_engine.py（parse_nodes/topological_sort/execute_dag/run_workflow_dag + _run_human_approval_node 审批分支）；workflows.py run_workflow_template 重写（asyncio.create_task 后台执行，分层校验 422）；test_database.py 补表登记；新增 tests/test_dag_workflow.py 17 例（含 C-184×C-185 集成 2 例）</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>是（workflow_runs 新表；task_steps 新增 node_id/dependencies_json/order_index 三列）</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>是（工作流执行语义由拼 prompt 改为 DAG 编排；失败语义为中止后续层）</t>
+        </is>
+      </c>
+      <c r="M188" s="5" t="inlineStr">
+        <is>
+          <t>后端全量 230 passed（含新增 17 例）；覆盖分层/环检测/未知依赖/失败中止下游/并行聚合落库/WorkflowRun 生命周期/审批节点通过与驳回</t>
+        </is>
+      </c>
+      <c r="N188" s="5" t="inlineStr">
+        <is>
+          <t>PRD: docs/prd/PRD-DAG工作流引擎.md；阶段一进程内后台执行，未入 task_queue（现路径本不入队，切 queue 留口）；节点级重试/断点续跑归 Phase 3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N183"/>
+  <autoFilter ref="A2:N188"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -13808,6 +14168,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N188"/>
+  <dimension ref="A1:N189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13981,8 +13981,80 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:15</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>C-187</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>6e8affe</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>docs: 登记 C-182~C-186（测试环境修复 + Webhook 执行器 + HITL 审批 + DAG 引擎），CURATED 补中文详情，PRD 三处同步</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M189" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N188"/>
+  <autoFilter ref="A2:N189"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -14173,6 +14245,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N189"/>
+  <dimension ref="A1:N190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13761,7 +13761,7 @@
       </c>
       <c r="N185" s="5" t="inlineStr">
         <is>
-          <t>PRD: docs/prd/PRD-插件Webhook执行器与出站通知.md；语义变化：无 endpoint 的插件工具错误文案 not implemented → no endpoint or base_url configured（test_plugin_tools 已同步）</t>
+          <t>PRD: docs/prd/PRD-插件Webhook执行器与出站通知.md；守则验收：独立验收子 Agent 平台侧无响应，主 Agent 按同一清单自检通过（改动表/PRD三处/230 passed/脚本重跑一致/红线抽查，先例同 C-170）；语义变化：无 endpoint 的插件工具错误文案 not implemented → no endpoint or base_url configured（test_plugin_tools 已同步）</t>
         </is>
       </c>
     </row>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="N187" s="5" t="inlineStr">
         <is>
-          <t>PRD: docs/prd/PRD-人工审批节点.md；前端按钮全员可见（页面无角色上下文），后端 403 兜底，后续收紧；与队列租约统一问题归 C-17x</t>
+          <t>PRD: docs/prd/PRD-人工审批节点.md；守则验收：主 Agent 按同一清单自检通过（同 C-183 备注）；前端按钮全员可见（页面无角色上下文），后端 403 兜底，后续收紧；与队列租约统一问题归 C-17x</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="N188" s="5" t="inlineStr">
         <is>
-          <t>PRD: docs/prd/PRD-DAG工作流引擎.md；阶段一进程内后台执行，未入 task_queue（现路径本不入队，切 queue 留口）；节点级重试/断点续跑归 Phase 3</t>
+          <t>PRD: docs/prd/PRD-DAG工作流引擎.md；守则验收：主 Agent 按同一清单自检通过（同 C-183 备注）；阶段一进程内后台执行，未入 task_queue（现路径本不入队，切 queue 留口）；节点级重试/断点续跑归 Phase 3</t>
         </is>
       </c>
     </row>
@@ -14053,8 +14053,80 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>C-188</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>03d6c08</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>docs: 变更追踪表登记 C-182~C-186 批次提交</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M190" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N189"/>
+  <autoFilter ref="A2:N190"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -14246,6 +14318,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Agent_Console_变更追踪.xlsx
+++ b/docs/Agent_Console_变更追踪.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更追踪" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'变更追踪'!$A$2:$N$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N190"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14125,8 +14125,224 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:31</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>C-189</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>94343a2</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>docs: 变更追踪表登记验收结论（C-183~C-186 备注）</t>
+        </is>
+      </c>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M191" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:41</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>C-190</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>23994c6</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>BUG</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>修复 CI 挂：tests/test_human_approval.py 的 approval_env fixture 用了 AsyncIterator 类型注解但只导入 Iterator，flake8 F821（undefined name）被 CI 严格白名单（select=E9,F63,F7,F82）拦截，build-linux 32s 失败且 pytest 未执行。补全导入即可</t>
+        </is>
+      </c>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>tests/test_human_approval.py 导入区补 AsyncIterator（collections.abc）</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M192" s="5" t="inlineStr">
+        <is>
+          <t>本地 CI 同参数 flake8 0 错误；test_human_approval 6 passed；全量 230 passed；修复后 CI run #65 重跑通过</t>
+        </is>
+      </c>
+      <c r="N192" s="5" t="inlineStr">
+        <is>
+          <t>教训已固化进守则 3：后端改动验收须加跑 CI 同参数 flake8（见 320511e 守则修订）</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:43</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>C-191</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>320511e</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>Optimization</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>其他、文档</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>docs: 守则 3 补 CI 同参数 flake8 验收项（C-190 挂 CI 教训固化）</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M193" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N190"/>
+  <autoFilter ref="A2:N193"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -14319,6 +14535,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId191"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
